--- a/design/Spis innych przedmiotów.xlsx
+++ b/design/Spis innych przedmiotów.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryczku\Documents\Godmist\design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{354AA341-0986-44F4-8905-16B28064E9DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBD835F8-CDA9-4C4C-A818-11C239583E65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Polski v2" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,6 @@
     <sheet name="Mikstury i Bomby" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -453,7 +452,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4269" uniqueCount="1500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4269" uniqueCount="1496">
   <si>
     <t>Nazwa przedmiotu</t>
   </si>
@@ -4709,12 +4708,6 @@
     <t>+3t</t>
   </si>
   <si>
-    <t>+4t</t>
-  </si>
-  <si>
-    <t>+5t</t>
-  </si>
-  <si>
     <t>Sumujemy siły efektów</t>
   </si>
   <si>
@@ -4743,12 +4736,6 @@
   </si>
   <si>
     <t>-3t</t>
-  </si>
-  <si>
-    <t>-4t</t>
-  </si>
-  <si>
-    <t>-5t</t>
   </si>
   <si>
     <t>Nieugiętości</t>
@@ -5667,72 +5654,72 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5856,10 +5843,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -25897,43 +25880,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A1" s="115" t="s">
+      <c r="A1" s="93" t="s">
         <v>1009</v>
       </c>
-      <c r="B1" s="113" t="s">
+      <c r="B1" s="95" t="s">
         <v>1010</v>
       </c>
-      <c r="C1" s="100" t="s">
+      <c r="C1" s="91" t="s">
         <v>1011</v>
       </c>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
-      <c r="F1" s="106"/>
-      <c r="G1" s="106"/>
-      <c r="H1" s="106"/>
-      <c r="I1" s="101"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="98"/>
+      <c r="H1" s="98"/>
+      <c r="I1" s="92"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A2" s="109"/>
-      <c r="B2" s="87"/>
-      <c r="C2" s="113" t="s">
+      <c r="A2" s="94"/>
+      <c r="B2" s="96"/>
+      <c r="C2" s="95" t="s">
         <v>1012</v>
       </c>
-      <c r="D2" s="100" t="s">
+      <c r="D2" s="91" t="s">
         <v>1013</v>
       </c>
-      <c r="E2" s="106"/>
-      <c r="F2" s="106"/>
-      <c r="G2" s="106"/>
-      <c r="H2" s="101"/>
-      <c r="I2" s="113" t="s">
+      <c r="E2" s="98"/>
+      <c r="F2" s="98"/>
+      <c r="G2" s="98"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="95" t="s">
         <v>1014</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A3" s="109"/>
-      <c r="B3" s="114"/>
-      <c r="C3" s="114"/>
+      <c r="A3" s="94"/>
+      <c r="B3" s="97"/>
+      <c r="C3" s="97"/>
       <c r="D3" s="35">
         <v>44206</v>
       </c>
@@ -25949,13 +25932,13 @@
       <c r="H3" s="36" t="s">
         <v>1017</v>
       </c>
-      <c r="I3" s="114"/>
+      <c r="I3" s="97"/>
     </row>
     <row r="4" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A4" s="116" t="s">
+      <c r="A4" s="99" t="s">
         <v>884</v>
       </c>
-      <c r="B4" s="116" t="s">
+      <c r="B4" s="99" t="s">
         <v>973</v>
       </c>
       <c r="C4" s="36" t="s">
@@ -25981,8 +25964,8 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A5" s="87"/>
-      <c r="B5" s="87"/>
+      <c r="A5" s="96"/>
+      <c r="B5" s="96"/>
       <c r="C5" s="36" t="s">
         <v>1024</v>
       </c>
@@ -26001,13 +25984,13 @@
       <c r="H5" s="36" t="s">
         <v>1029</v>
       </c>
-      <c r="I5" s="113">
+      <c r="I5" s="95">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A6" s="87"/>
-      <c r="B6" s="87"/>
+      <c r="A6" s="96"/>
+      <c r="B6" s="96"/>
       <c r="C6" s="36" t="s">
         <v>1030</v>
       </c>
@@ -26026,11 +26009,11 @@
       <c r="H6" s="36" t="s">
         <v>1035</v>
       </c>
-      <c r="I6" s="87"/>
+      <c r="I6" s="96"/>
     </row>
     <row r="7" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A7" s="87"/>
-      <c r="B7" s="87"/>
+      <c r="A7" s="96"/>
+      <c r="B7" s="96"/>
       <c r="C7" s="38" t="s">
         <v>1036</v>
       </c>
@@ -26049,72 +26032,72 @@
       <c r="H7" s="36" t="s">
         <v>1041</v>
       </c>
-      <c r="I7" s="114"/>
+      <c r="I7" s="97"/>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A8" s="87"/>
-      <c r="B8" s="87"/>
+      <c r="A8" s="96"/>
+      <c r="B8" s="96"/>
       <c r="C8" s="38" t="s">
         <v>1042</v>
       </c>
       <c r="D8" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E8" s="100" t="s">
+      <c r="E8" s="91" t="s">
         <v>1044</v>
       </c>
-      <c r="F8" s="101"/>
-      <c r="G8" s="100" t="s">
+      <c r="F8" s="92"/>
+      <c r="G8" s="91" t="s">
         <v>1045</v>
       </c>
-      <c r="H8" s="101"/>
+      <c r="H8" s="92"/>
       <c r="I8" s="38">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A9" s="87"/>
-      <c r="B9" s="87"/>
+      <c r="A9" s="96"/>
+      <c r="B9" s="96"/>
       <c r="C9" s="38" t="s">
         <v>1042</v>
       </c>
-      <c r="D9" s="100" t="s">
+      <c r="D9" s="91" t="s">
         <v>1046</v>
       </c>
-      <c r="E9" s="101"/>
-      <c r="F9" s="100" t="s">
+      <c r="E9" s="92"/>
+      <c r="F9" s="91" t="s">
         <v>1047</v>
       </c>
-      <c r="G9" s="101"/>
+      <c r="G9" s="92"/>
       <c r="H9" s="36" t="s">
         <v>1048</v>
       </c>
-      <c r="I9" s="113">
+      <c r="I9" s="95">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A10" s="87"/>
-      <c r="B10" s="87"/>
+      <c r="A10" s="96"/>
+      <c r="B10" s="96"/>
       <c r="C10" s="38" t="s">
         <v>1049</v>
       </c>
-      <c r="D10" s="100" t="s">
+      <c r="D10" s="91" t="s">
         <v>1050</v>
       </c>
-      <c r="E10" s="101"/>
-      <c r="F10" s="100" t="s">
+      <c r="E10" s="92"/>
+      <c r="F10" s="91" t="s">
         <v>1051</v>
       </c>
-      <c r="G10" s="101"/>
+      <c r="G10" s="92"/>
       <c r="H10" s="36" t="s">
         <v>1052</v>
       </c>
-      <c r="I10" s="114"/>
+      <c r="I10" s="97"/>
     </row>
     <row r="11" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A11" s="87"/>
-      <c r="B11" s="87"/>
+      <c r="A11" s="96"/>
+      <c r="B11" s="96"/>
       <c r="C11" s="36" t="s">
         <v>1053</v>
       </c>
@@ -26124,10 +26107,10 @@
       <c r="E11" s="36" t="s">
         <v>1054</v>
       </c>
-      <c r="F11" s="100" t="s">
+      <c r="F11" s="91" t="s">
         <v>1055</v>
       </c>
-      <c r="G11" s="101"/>
+      <c r="G11" s="92"/>
       <c r="H11" s="36" t="s">
         <v>1056</v>
       </c>
@@ -26136,84 +26119,84 @@
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A12" s="87"/>
-      <c r="B12" s="87"/>
+      <c r="A12" s="96"/>
+      <c r="B12" s="96"/>
       <c r="C12" s="36" t="s">
         <v>1057</v>
       </c>
       <c r="D12" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E12" s="100" t="s">
+      <c r="E12" s="91" t="s">
         <v>1058</v>
       </c>
-      <c r="F12" s="106"/>
-      <c r="G12" s="106"/>
-      <c r="H12" s="101"/>
+      <c r="F12" s="98"/>
+      <c r="G12" s="98"/>
+      <c r="H12" s="92"/>
       <c r="I12" s="38">
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A13" s="87"/>
-      <c r="B13" s="87"/>
+      <c r="A13" s="96"/>
+      <c r="B13" s="96"/>
       <c r="C13" s="36" t="s">
         <v>1059</v>
       </c>
       <c r="D13" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E13" s="100" t="s">
+      <c r="E13" s="91" t="s">
         <v>1060</v>
       </c>
-      <c r="F13" s="106"/>
-      <c r="G13" s="106"/>
-      <c r="H13" s="101"/>
+      <c r="F13" s="98"/>
+      <c r="G13" s="98"/>
+      <c r="H13" s="92"/>
       <c r="I13" s="38">
         <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A14" s="87"/>
-      <c r="B14" s="87"/>
+      <c r="A14" s="96"/>
+      <c r="B14" s="96"/>
       <c r="C14" s="36" t="s">
         <v>1061</v>
       </c>
-      <c r="D14" s="100" t="s">
+      <c r="D14" s="91" t="s">
         <v>1062</v>
       </c>
-      <c r="E14" s="106"/>
-      <c r="F14" s="106"/>
-      <c r="G14" s="106"/>
-      <c r="H14" s="101"/>
+      <c r="E14" s="98"/>
+      <c r="F14" s="98"/>
+      <c r="G14" s="98"/>
+      <c r="H14" s="92"/>
       <c r="I14" s="38">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A15" s="114"/>
-      <c r="B15" s="114"/>
+      <c r="A15" s="97"/>
+      <c r="B15" s="97"/>
       <c r="C15" s="37" t="s">
         <v>1063</v>
       </c>
-      <c r="D15" s="94" t="s">
+      <c r="D15" s="103" t="s">
         <v>1043</v>
       </c>
-      <c r="E15" s="95"/>
-      <c r="F15" s="94" t="s">
+      <c r="E15" s="104"/>
+      <c r="F15" s="103" t="s">
         <v>1064</v>
       </c>
-      <c r="G15" s="96"/>
-      <c r="H15" s="95"/>
+      <c r="G15" s="115"/>
+      <c r="H15" s="104"/>
       <c r="I15" s="33">
         <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A16" s="83" t="s">
+      <c r="A16" s="112" t="s">
         <v>896</v>
       </c>
-      <c r="B16" s="83" t="s">
+      <c r="B16" s="112" t="s">
         <v>975</v>
       </c>
       <c r="C16" s="39" t="s">
@@ -26239,8 +26222,8 @@
       </c>
     </row>
     <row r="17" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A17" s="84"/>
-      <c r="B17" s="84"/>
+      <c r="A17" s="90"/>
+      <c r="B17" s="90"/>
       <c r="C17" s="41" t="s">
         <v>1024</v>
       </c>
@@ -26259,13 +26242,13 @@
       <c r="H17" s="41" t="s">
         <v>1069</v>
       </c>
-      <c r="I17" s="99">
+      <c r="I17" s="89">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A18" s="84"/>
-      <c r="B18" s="84"/>
+      <c r="A18" s="90"/>
+      <c r="B18" s="90"/>
       <c r="C18" s="41" t="s">
         <v>1030</v>
       </c>
@@ -26284,11 +26267,11 @@
       <c r="H18" s="41" t="s">
         <v>1074</v>
       </c>
-      <c r="I18" s="84"/>
+      <c r="I18" s="90"/>
     </row>
     <row r="19" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A19" s="84"/>
-      <c r="B19" s="84"/>
+      <c r="A19" s="90"/>
+      <c r="B19" s="90"/>
       <c r="C19" s="43" t="s">
         <v>1036</v>
       </c>
@@ -26307,72 +26290,72 @@
       <c r="H19" s="41" t="s">
         <v>1079</v>
       </c>
-      <c r="I19" s="93"/>
+      <c r="I19" s="84"/>
     </row>
     <row r="20" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A20" s="84"/>
-      <c r="B20" s="84"/>
+      <c r="A20" s="90"/>
+      <c r="B20" s="90"/>
       <c r="C20" s="43" t="s">
         <v>1042</v>
       </c>
       <c r="D20" s="41" t="s">
         <v>1043</v>
       </c>
-      <c r="E20" s="91" t="s">
+      <c r="E20" s="83" t="s">
         <v>1080</v>
       </c>
-      <c r="F20" s="93"/>
-      <c r="G20" s="91" t="s">
+      <c r="F20" s="84"/>
+      <c r="G20" s="83" t="s">
         <v>1081</v>
       </c>
-      <c r="H20" s="93"/>
+      <c r="H20" s="84"/>
       <c r="I20" s="43">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A21" s="84"/>
-      <c r="B21" s="84"/>
+      <c r="A21" s="90"/>
+      <c r="B21" s="90"/>
       <c r="C21" s="43" t="s">
         <v>1042</v>
       </c>
-      <c r="D21" s="91" t="s">
+      <c r="D21" s="83" t="s">
         <v>1082</v>
       </c>
-      <c r="E21" s="93"/>
-      <c r="F21" s="91" t="s">
+      <c r="E21" s="84"/>
+      <c r="F21" s="83" t="s">
         <v>1083</v>
       </c>
-      <c r="G21" s="93"/>
+      <c r="G21" s="84"/>
       <c r="H21" s="41" t="s">
         <v>1084</v>
       </c>
-      <c r="I21" s="99">
+      <c r="I21" s="89">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A22" s="84"/>
-      <c r="B22" s="84"/>
+      <c r="A22" s="90"/>
+      <c r="B22" s="90"/>
       <c r="C22" s="43" t="s">
         <v>1049</v>
       </c>
-      <c r="D22" s="91" t="s">
+      <c r="D22" s="83" t="s">
         <v>1085</v>
       </c>
-      <c r="E22" s="93"/>
-      <c r="F22" s="91" t="s">
+      <c r="E22" s="84"/>
+      <c r="F22" s="83" t="s">
         <v>1086</v>
       </c>
-      <c r="G22" s="93"/>
+      <c r="G22" s="84"/>
       <c r="H22" s="41" t="s">
         <v>1087</v>
       </c>
-      <c r="I22" s="93"/>
+      <c r="I22" s="84"/>
     </row>
     <row r="23" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A23" s="84"/>
-      <c r="B23" s="84"/>
+      <c r="A23" s="90"/>
+      <c r="B23" s="90"/>
       <c r="C23" s="41" t="s">
         <v>1053</v>
       </c>
@@ -26382,10 +26365,10 @@
       <c r="E23" s="41" t="s">
         <v>1054</v>
       </c>
-      <c r="F23" s="91" t="s">
+      <c r="F23" s="83" t="s">
         <v>1055</v>
       </c>
-      <c r="G23" s="93"/>
+      <c r="G23" s="84"/>
       <c r="H23" s="41" t="s">
         <v>1056</v>
       </c>
@@ -26394,84 +26377,84 @@
       </c>
     </row>
     <row r="24" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A24" s="84"/>
-      <c r="B24" s="84"/>
+      <c r="A24" s="90"/>
+      <c r="B24" s="90"/>
       <c r="C24" s="41" t="s">
         <v>1057</v>
       </c>
       <c r="D24" s="41" t="s">
         <v>1043</v>
       </c>
-      <c r="E24" s="91" t="s">
+      <c r="E24" s="83" t="s">
         <v>1088</v>
       </c>
-      <c r="F24" s="92"/>
-      <c r="G24" s="92"/>
-      <c r="H24" s="93"/>
+      <c r="F24" s="85"/>
+      <c r="G24" s="85"/>
+      <c r="H24" s="84"/>
       <c r="I24" s="43">
         <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A25" s="84"/>
-      <c r="B25" s="84"/>
+      <c r="A25" s="90"/>
+      <c r="B25" s="90"/>
       <c r="C25" s="41" t="s">
         <v>1059</v>
       </c>
       <c r="D25" s="41" t="s">
         <v>1043</v>
       </c>
-      <c r="E25" s="91" t="s">
+      <c r="E25" s="83" t="s">
         <v>1089</v>
       </c>
-      <c r="F25" s="92"/>
-      <c r="G25" s="92"/>
-      <c r="H25" s="93"/>
+      <c r="F25" s="85"/>
+      <c r="G25" s="85"/>
+      <c r="H25" s="84"/>
       <c r="I25" s="43">
         <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A26" s="84"/>
-      <c r="B26" s="84"/>
+      <c r="A26" s="90"/>
+      <c r="B26" s="90"/>
       <c r="C26" s="41" t="s">
         <v>1061</v>
       </c>
-      <c r="D26" s="91" t="s">
+      <c r="D26" s="83" t="s">
         <v>1090</v>
       </c>
-      <c r="E26" s="92"/>
-      <c r="F26" s="92"/>
-      <c r="G26" s="92"/>
-      <c r="H26" s="93"/>
+      <c r="E26" s="85"/>
+      <c r="F26" s="85"/>
+      <c r="G26" s="85"/>
+      <c r="H26" s="84"/>
       <c r="I26" s="43">
         <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A27" s="85"/>
-      <c r="B27" s="85"/>
+      <c r="A27" s="87"/>
+      <c r="B27" s="87"/>
       <c r="C27" s="44" t="s">
         <v>1063</v>
       </c>
-      <c r="D27" s="97" t="s">
+      <c r="D27" s="86" t="s">
         <v>1043</v>
       </c>
-      <c r="E27" s="85"/>
-      <c r="F27" s="97" t="s">
+      <c r="E27" s="87"/>
+      <c r="F27" s="86" t="s">
         <v>1091</v>
       </c>
-      <c r="G27" s="98"/>
-      <c r="H27" s="85"/>
+      <c r="G27" s="88"/>
+      <c r="H27" s="87"/>
       <c r="I27" s="45">
         <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A28" s="83" t="s">
+      <c r="A28" s="112" t="s">
         <v>899</v>
       </c>
-      <c r="B28" s="83" t="s">
+      <c r="B28" s="112" t="s">
         <v>976</v>
       </c>
       <c r="C28" s="39" t="s">
@@ -26497,8 +26480,8 @@
       </c>
     </row>
     <row r="29" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A29" s="84"/>
-      <c r="B29" s="84"/>
+      <c r="A29" s="90"/>
+      <c r="B29" s="90"/>
       <c r="C29" s="41" t="s">
         <v>1024</v>
       </c>
@@ -26517,13 +26500,13 @@
       <c r="H29" s="41" t="s">
         <v>1096</v>
       </c>
-      <c r="I29" s="99">
+      <c r="I29" s="89">
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A30" s="84"/>
-      <c r="B30" s="84"/>
+      <c r="A30" s="90"/>
+      <c r="B30" s="90"/>
       <c r="C30" s="41" t="s">
         <v>1030</v>
       </c>
@@ -26542,11 +26525,11 @@
       <c r="H30" s="41" t="s">
         <v>1101</v>
       </c>
-      <c r="I30" s="84"/>
+      <c r="I30" s="90"/>
     </row>
     <row r="31" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A31" s="84"/>
-      <c r="B31" s="84"/>
+      <c r="A31" s="90"/>
+      <c r="B31" s="90"/>
       <c r="C31" s="43" t="s">
         <v>1036</v>
       </c>
@@ -26565,72 +26548,72 @@
       <c r="H31" s="41" t="s">
         <v>1106</v>
       </c>
-      <c r="I31" s="93"/>
+      <c r="I31" s="84"/>
     </row>
     <row r="32" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A32" s="84"/>
-      <c r="B32" s="84"/>
+      <c r="A32" s="90"/>
+      <c r="B32" s="90"/>
       <c r="C32" s="43" t="s">
         <v>1042</v>
       </c>
       <c r="D32" s="41" t="s">
         <v>1043</v>
       </c>
-      <c r="E32" s="91" t="s">
+      <c r="E32" s="83" t="s">
         <v>1107</v>
       </c>
-      <c r="F32" s="93"/>
-      <c r="G32" s="100" t="s">
+      <c r="F32" s="84"/>
+      <c r="G32" s="91" t="s">
         <v>1045</v>
       </c>
-      <c r="H32" s="101"/>
+      <c r="H32" s="92"/>
       <c r="I32" s="43">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A33" s="84"/>
-      <c r="B33" s="84"/>
+      <c r="A33" s="90"/>
+      <c r="B33" s="90"/>
       <c r="C33" s="43" t="s">
         <v>1042</v>
       </c>
-      <c r="D33" s="91" t="s">
+      <c r="D33" s="83" t="s">
         <v>1108</v>
       </c>
-      <c r="E33" s="93"/>
-      <c r="F33" s="91" t="s">
+      <c r="E33" s="84"/>
+      <c r="F33" s="83" t="s">
         <v>1109</v>
       </c>
-      <c r="G33" s="93"/>
+      <c r="G33" s="84"/>
       <c r="H33" s="41" t="s">
         <v>1110</v>
       </c>
-      <c r="I33" s="99">
+      <c r="I33" s="89">
         <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A34" s="84"/>
-      <c r="B34" s="84"/>
+      <c r="A34" s="90"/>
+      <c r="B34" s="90"/>
       <c r="C34" s="43" t="s">
         <v>1049</v>
       </c>
-      <c r="D34" s="91" t="s">
+      <c r="D34" s="83" t="s">
         <v>1111</v>
       </c>
-      <c r="E34" s="93"/>
-      <c r="F34" s="91" t="s">
+      <c r="E34" s="84"/>
+      <c r="F34" s="83" t="s">
         <v>1112</v>
       </c>
-      <c r="G34" s="93"/>
+      <c r="G34" s="84"/>
       <c r="H34" s="41" t="s">
         <v>1113</v>
       </c>
-      <c r="I34" s="93"/>
+      <c r="I34" s="84"/>
     </row>
     <row r="35" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A35" s="84"/>
-      <c r="B35" s="84"/>
+      <c r="A35" s="90"/>
+      <c r="B35" s="90"/>
       <c r="C35" s="41" t="s">
         <v>1053</v>
       </c>
@@ -26640,10 +26623,10 @@
       <c r="E35" s="41" t="s">
         <v>1054</v>
       </c>
-      <c r="F35" s="91" t="s">
+      <c r="F35" s="83" t="s">
         <v>1055</v>
       </c>
-      <c r="G35" s="93"/>
+      <c r="G35" s="84"/>
       <c r="H35" s="41" t="s">
         <v>1056</v>
       </c>
@@ -26652,84 +26635,84 @@
       </c>
     </row>
     <row r="36" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A36" s="84"/>
-      <c r="B36" s="84"/>
+      <c r="A36" s="90"/>
+      <c r="B36" s="90"/>
       <c r="C36" s="41" t="s">
         <v>1057</v>
       </c>
       <c r="D36" s="41" t="s">
         <v>1043</v>
       </c>
-      <c r="E36" s="91" t="s">
+      <c r="E36" s="83" t="s">
         <v>1114</v>
       </c>
-      <c r="F36" s="92"/>
-      <c r="G36" s="92"/>
-      <c r="H36" s="93"/>
+      <c r="F36" s="85"/>
+      <c r="G36" s="85"/>
+      <c r="H36" s="84"/>
       <c r="I36" s="43">
         <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A37" s="84"/>
-      <c r="B37" s="84"/>
+      <c r="A37" s="90"/>
+      <c r="B37" s="90"/>
       <c r="C37" s="41" t="s">
         <v>1059</v>
       </c>
       <c r="D37" s="41" t="s">
         <v>1043</v>
       </c>
-      <c r="E37" s="91" t="s">
+      <c r="E37" s="83" t="s">
         <v>1089</v>
       </c>
-      <c r="F37" s="92"/>
-      <c r="G37" s="92"/>
-      <c r="H37" s="93"/>
+      <c r="F37" s="85"/>
+      <c r="G37" s="85"/>
+      <c r="H37" s="84"/>
       <c r="I37" s="43">
         <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A38" s="84"/>
-      <c r="B38" s="84"/>
+      <c r="A38" s="90"/>
+      <c r="B38" s="90"/>
       <c r="C38" s="41" t="s">
         <v>1061</v>
       </c>
-      <c r="D38" s="91" t="s">
+      <c r="D38" s="83" t="s">
         <v>1115</v>
       </c>
-      <c r="E38" s="92"/>
-      <c r="F38" s="92"/>
-      <c r="G38" s="92"/>
-      <c r="H38" s="93"/>
+      <c r="E38" s="85"/>
+      <c r="F38" s="85"/>
+      <c r="G38" s="85"/>
+      <c r="H38" s="84"/>
       <c r="I38" s="43">
         <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A39" s="85"/>
-      <c r="B39" s="85"/>
+      <c r="A39" s="87"/>
+      <c r="B39" s="87"/>
       <c r="C39" s="44" t="s">
         <v>1063</v>
       </c>
-      <c r="D39" s="97" t="s">
+      <c r="D39" s="86" t="s">
         <v>1043</v>
       </c>
-      <c r="E39" s="85"/>
-      <c r="F39" s="97" t="s">
+      <c r="E39" s="87"/>
+      <c r="F39" s="86" t="s">
         <v>1116</v>
       </c>
-      <c r="G39" s="98"/>
-      <c r="H39" s="85"/>
+      <c r="G39" s="88"/>
+      <c r="H39" s="87"/>
       <c r="I39" s="45">
         <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A40" s="83" t="s">
+      <c r="A40" s="112" t="s">
         <v>887</v>
       </c>
-      <c r="B40" s="83" t="s">
+      <c r="B40" s="112" t="s">
         <v>977</v>
       </c>
       <c r="C40" s="39" t="s">
@@ -26755,8 +26738,8 @@
       </c>
     </row>
     <row r="41" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A41" s="84"/>
-      <c r="B41" s="84"/>
+      <c r="A41" s="90"/>
+      <c r="B41" s="90"/>
       <c r="C41" s="41" t="s">
         <v>1024</v>
       </c>
@@ -26775,13 +26758,13 @@
       <c r="H41" s="41" t="s">
         <v>1120</v>
       </c>
-      <c r="I41" s="99">
+      <c r="I41" s="89">
         <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A42" s="84"/>
-      <c r="B42" s="84"/>
+      <c r="A42" s="90"/>
+      <c r="B42" s="90"/>
       <c r="C42" s="41" t="s">
         <v>1030</v>
       </c>
@@ -26800,11 +26783,11 @@
       <c r="H42" s="41" t="s">
         <v>1124</v>
       </c>
-      <c r="I42" s="84"/>
+      <c r="I42" s="90"/>
     </row>
     <row r="43" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A43" s="84"/>
-      <c r="B43" s="84"/>
+      <c r="A43" s="90"/>
+      <c r="B43" s="90"/>
       <c r="C43" s="43" t="s">
         <v>1036</v>
       </c>
@@ -26823,72 +26806,72 @@
       <c r="H43" s="41" t="s">
         <v>1128</v>
       </c>
-      <c r="I43" s="93"/>
+      <c r="I43" s="84"/>
     </row>
     <row r="44" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A44" s="84"/>
-      <c r="B44" s="84"/>
+      <c r="A44" s="90"/>
+      <c r="B44" s="90"/>
       <c r="C44" s="43" t="s">
         <v>1042</v>
       </c>
       <c r="D44" s="41" t="s">
         <v>1043</v>
       </c>
-      <c r="E44" s="91" t="s">
+      <c r="E44" s="83" t="s">
         <v>1129</v>
       </c>
-      <c r="F44" s="93"/>
-      <c r="G44" s="100" t="s">
+      <c r="F44" s="84"/>
+      <c r="G44" s="91" t="s">
         <v>1130</v>
       </c>
-      <c r="H44" s="101"/>
+      <c r="H44" s="92"/>
       <c r="I44" s="43">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A45" s="84"/>
-      <c r="B45" s="84"/>
+      <c r="A45" s="90"/>
+      <c r="B45" s="90"/>
       <c r="C45" s="43" t="s">
         <v>1042</v>
       </c>
-      <c r="D45" s="91" t="s">
+      <c r="D45" s="83" t="s">
         <v>1131</v>
       </c>
-      <c r="E45" s="93"/>
-      <c r="F45" s="91" t="s">
+      <c r="E45" s="84"/>
+      <c r="F45" s="83" t="s">
         <v>1132</v>
       </c>
-      <c r="G45" s="93"/>
+      <c r="G45" s="84"/>
       <c r="H45" s="41" t="s">
         <v>1133</v>
       </c>
-      <c r="I45" s="99">
+      <c r="I45" s="89">
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A46" s="84"/>
-      <c r="B46" s="84"/>
+      <c r="A46" s="90"/>
+      <c r="B46" s="90"/>
       <c r="C46" s="43" t="s">
         <v>1049</v>
       </c>
-      <c r="D46" s="91" t="s">
+      <c r="D46" s="83" t="s">
         <v>1134</v>
       </c>
-      <c r="E46" s="93"/>
-      <c r="F46" s="91" t="s">
+      <c r="E46" s="84"/>
+      <c r="F46" s="83" t="s">
         <v>1135</v>
       </c>
-      <c r="G46" s="93"/>
+      <c r="G46" s="84"/>
       <c r="H46" s="41" t="s">
         <v>1136</v>
       </c>
-      <c r="I46" s="93"/>
+      <c r="I46" s="84"/>
     </row>
     <row r="47" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A47" s="84"/>
-      <c r="B47" s="84"/>
+      <c r="A47" s="90"/>
+      <c r="B47" s="90"/>
       <c r="C47" s="41" t="s">
         <v>1053</v>
       </c>
@@ -26898,10 +26881,10 @@
       <c r="E47" s="41" t="s">
         <v>1054</v>
       </c>
-      <c r="F47" s="91" t="s">
+      <c r="F47" s="83" t="s">
         <v>1055</v>
       </c>
-      <c r="G47" s="93"/>
+      <c r="G47" s="84"/>
       <c r="H47" s="41" t="s">
         <v>1056</v>
       </c>
@@ -26910,84 +26893,84 @@
       </c>
     </row>
     <row r="48" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A48" s="84"/>
-      <c r="B48" s="84"/>
+      <c r="A48" s="90"/>
+      <c r="B48" s="90"/>
       <c r="C48" s="41" t="s">
         <v>1057</v>
       </c>
       <c r="D48" s="41" t="s">
         <v>1043</v>
       </c>
-      <c r="E48" s="91" t="s">
+      <c r="E48" s="83" t="s">
         <v>1137</v>
       </c>
-      <c r="F48" s="92"/>
-      <c r="G48" s="92"/>
-      <c r="H48" s="93"/>
+      <c r="F48" s="85"/>
+      <c r="G48" s="85"/>
+      <c r="H48" s="84"/>
       <c r="I48" s="43">
         <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A49" s="84"/>
-      <c r="B49" s="84"/>
+      <c r="A49" s="90"/>
+      <c r="B49" s="90"/>
       <c r="C49" s="41" t="s">
         <v>1059</v>
       </c>
       <c r="D49" s="41" t="s">
         <v>1043</v>
       </c>
-      <c r="E49" s="91" t="s">
+      <c r="E49" s="83" t="s">
         <v>1060</v>
       </c>
-      <c r="F49" s="92"/>
-      <c r="G49" s="92"/>
-      <c r="H49" s="93"/>
+      <c r="F49" s="85"/>
+      <c r="G49" s="85"/>
+      <c r="H49" s="84"/>
       <c r="I49" s="43">
         <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A50" s="84"/>
-      <c r="B50" s="84"/>
+      <c r="A50" s="90"/>
+      <c r="B50" s="90"/>
       <c r="C50" s="41" t="s">
         <v>1061</v>
       </c>
-      <c r="D50" s="91" t="s">
+      <c r="D50" s="83" t="s">
         <v>1138</v>
       </c>
-      <c r="E50" s="92"/>
-      <c r="F50" s="92"/>
-      <c r="G50" s="92"/>
-      <c r="H50" s="93"/>
+      <c r="E50" s="85"/>
+      <c r="F50" s="85"/>
+      <c r="G50" s="85"/>
+      <c r="H50" s="84"/>
       <c r="I50" s="43">
         <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A51" s="85"/>
-      <c r="B51" s="85"/>
+      <c r="A51" s="87"/>
+      <c r="B51" s="87"/>
       <c r="C51" s="44" t="s">
         <v>1063</v>
       </c>
-      <c r="D51" s="97" t="s">
+      <c r="D51" s="86" t="s">
         <v>1043</v>
       </c>
-      <c r="E51" s="85"/>
-      <c r="F51" s="97" t="s">
+      <c r="E51" s="87"/>
+      <c r="F51" s="86" t="s">
         <v>1139</v>
       </c>
-      <c r="G51" s="98"/>
-      <c r="H51" s="85"/>
+      <c r="G51" s="88"/>
+      <c r="H51" s="87"/>
       <c r="I51" s="45">
         <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A52" s="83" t="s">
+      <c r="A52" s="112" t="s">
         <v>893</v>
       </c>
-      <c r="B52" s="83" t="s">
+      <c r="B52" s="112" t="s">
         <v>978</v>
       </c>
       <c r="C52" s="39" t="s">
@@ -27013,8 +26996,8 @@
       </c>
     </row>
     <row r="53" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A53" s="84"/>
-      <c r="B53" s="84"/>
+      <c r="A53" s="90"/>
+      <c r="B53" s="90"/>
       <c r="C53" s="41" t="s">
         <v>1024</v>
       </c>
@@ -27033,13 +27016,13 @@
       <c r="H53" s="41" t="s">
         <v>1143</v>
       </c>
-      <c r="I53" s="99">
+      <c r="I53" s="89">
         <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A54" s="84"/>
-      <c r="B54" s="84"/>
+      <c r="A54" s="90"/>
+      <c r="B54" s="90"/>
       <c r="C54" s="41" t="s">
         <v>1030</v>
       </c>
@@ -27058,11 +27041,11 @@
       <c r="H54" s="41" t="s">
         <v>1147</v>
       </c>
-      <c r="I54" s="84"/>
+      <c r="I54" s="90"/>
     </row>
     <row r="55" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A55" s="84"/>
-      <c r="B55" s="84"/>
+      <c r="A55" s="90"/>
+      <c r="B55" s="90"/>
       <c r="C55" s="43" t="s">
         <v>1036</v>
       </c>
@@ -27081,72 +27064,72 @@
       <c r="H55" s="41" t="s">
         <v>1151</v>
       </c>
-      <c r="I55" s="93"/>
+      <c r="I55" s="84"/>
     </row>
     <row r="56" spans="1:9" ht="12.75">
-      <c r="A56" s="84"/>
-      <c r="B56" s="84"/>
+      <c r="A56" s="90"/>
+      <c r="B56" s="90"/>
       <c r="C56" s="43" t="s">
         <v>1042</v>
       </c>
       <c r="D56" s="41" t="s">
         <v>1043</v>
       </c>
-      <c r="E56" s="91" t="s">
+      <c r="E56" s="83" t="s">
         <v>1080</v>
       </c>
-      <c r="F56" s="93"/>
-      <c r="G56" s="100" t="s">
+      <c r="F56" s="84"/>
+      <c r="G56" s="91" t="s">
         <v>1152</v>
       </c>
-      <c r="H56" s="101"/>
+      <c r="H56" s="92"/>
       <c r="I56" s="43">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="25.5">
-      <c r="A57" s="84"/>
-      <c r="B57" s="84"/>
+      <c r="A57" s="90"/>
+      <c r="B57" s="90"/>
       <c r="C57" s="43" t="s">
         <v>1042</v>
       </c>
-      <c r="D57" s="91" t="s">
+      <c r="D57" s="83" t="s">
         <v>1153</v>
       </c>
-      <c r="E57" s="93"/>
-      <c r="F57" s="91" t="s">
+      <c r="E57" s="84"/>
+      <c r="F57" s="83" t="s">
         <v>1154</v>
       </c>
-      <c r="G57" s="93"/>
+      <c r="G57" s="84"/>
       <c r="H57" s="41" t="s">
         <v>1155</v>
       </c>
-      <c r="I57" s="99">
+      <c r="I57" s="89">
         <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="25.5">
-      <c r="A58" s="84"/>
-      <c r="B58" s="84"/>
+      <c r="A58" s="90"/>
+      <c r="B58" s="90"/>
       <c r="C58" s="43" t="s">
         <v>1049</v>
       </c>
-      <c r="D58" s="91" t="s">
+      <c r="D58" s="83" t="s">
         <v>1156</v>
       </c>
-      <c r="E58" s="93"/>
-      <c r="F58" s="91" t="s">
+      <c r="E58" s="84"/>
+      <c r="F58" s="83" t="s">
         <v>1157</v>
       </c>
-      <c r="G58" s="93"/>
+      <c r="G58" s="84"/>
       <c r="H58" s="41" t="s">
         <v>1158</v>
       </c>
-      <c r="I58" s="93"/>
+      <c r="I58" s="84"/>
     </row>
     <row r="59" spans="1:9" ht="12.75">
-      <c r="A59" s="84"/>
-      <c r="B59" s="84"/>
+      <c r="A59" s="90"/>
+      <c r="B59" s="90"/>
       <c r="C59" s="41" t="s">
         <v>1053</v>
       </c>
@@ -27156,10 +27139,10 @@
       <c r="E59" s="41" t="s">
         <v>1054</v>
       </c>
-      <c r="F59" s="91" t="s">
+      <c r="F59" s="83" t="s">
         <v>1055</v>
       </c>
-      <c r="G59" s="93"/>
+      <c r="G59" s="84"/>
       <c r="H59" s="41" t="s">
         <v>1056</v>
       </c>
@@ -27168,84 +27151,84 @@
       </c>
     </row>
     <row r="60" spans="1:9" ht="12.75">
-      <c r="A60" s="84"/>
-      <c r="B60" s="84"/>
+      <c r="A60" s="90"/>
+      <c r="B60" s="90"/>
       <c r="C60" s="41" t="s">
         <v>1057</v>
       </c>
       <c r="D60" s="41" t="s">
         <v>1043</v>
       </c>
-      <c r="E60" s="91" t="s">
+      <c r="E60" s="83" t="s">
         <v>1159</v>
       </c>
-      <c r="F60" s="92"/>
-      <c r="G60" s="92"/>
-      <c r="H60" s="93"/>
+      <c r="F60" s="85"/>
+      <c r="G60" s="85"/>
+      <c r="H60" s="84"/>
       <c r="I60" s="43">
         <v>2</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="12.75">
-      <c r="A61" s="84"/>
-      <c r="B61" s="84"/>
+      <c r="A61" s="90"/>
+      <c r="B61" s="90"/>
       <c r="C61" s="41" t="s">
         <v>1059</v>
       </c>
       <c r="D61" s="41" t="s">
         <v>1043</v>
       </c>
-      <c r="E61" s="91" t="s">
+      <c r="E61" s="83" t="s">
         <v>1060</v>
       </c>
-      <c r="F61" s="92"/>
-      <c r="G61" s="92"/>
-      <c r="H61" s="93"/>
+      <c r="F61" s="85"/>
+      <c r="G61" s="85"/>
+      <c r="H61" s="84"/>
       <c r="I61" s="43">
         <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="12.75">
-      <c r="A62" s="84"/>
-      <c r="B62" s="84"/>
+      <c r="A62" s="90"/>
+      <c r="B62" s="90"/>
       <c r="C62" s="41" t="s">
         <v>1061</v>
       </c>
-      <c r="D62" s="91" t="s">
+      <c r="D62" s="83" t="s">
         <v>1160</v>
       </c>
-      <c r="E62" s="92"/>
-      <c r="F62" s="92"/>
-      <c r="G62" s="92"/>
-      <c r="H62" s="93"/>
+      <c r="E62" s="85"/>
+      <c r="F62" s="85"/>
+      <c r="G62" s="85"/>
+      <c r="H62" s="84"/>
       <c r="I62" s="43">
         <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="12.75">
-      <c r="A63" s="85"/>
-      <c r="B63" s="85"/>
+      <c r="A63" s="87"/>
+      <c r="B63" s="87"/>
       <c r="C63" s="44" t="s">
         <v>1063</v>
       </c>
-      <c r="D63" s="97" t="s">
+      <c r="D63" s="86" t="s">
         <v>1043</v>
       </c>
-      <c r="E63" s="85"/>
-      <c r="F63" s="97" t="s">
+      <c r="E63" s="87"/>
+      <c r="F63" s="86" t="s">
         <v>1139</v>
       </c>
-      <c r="G63" s="98"/>
-      <c r="H63" s="85"/>
+      <c r="G63" s="88"/>
+      <c r="H63" s="87"/>
       <c r="I63" s="45">
         <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="12.75">
-      <c r="A64" s="83" t="s">
+      <c r="A64" s="112" t="s">
         <v>890</v>
       </c>
-      <c r="B64" s="83" t="s">
+      <c r="B64" s="112" t="s">
         <v>979</v>
       </c>
       <c r="C64" s="39" t="s">
@@ -27271,8 +27254,8 @@
       </c>
     </row>
     <row r="65" spans="1:9" ht="51">
-      <c r="A65" s="84"/>
-      <c r="B65" s="84"/>
+      <c r="A65" s="90"/>
+      <c r="B65" s="90"/>
       <c r="C65" s="41" t="s">
         <v>1024</v>
       </c>
@@ -27291,13 +27274,13 @@
       <c r="H65" s="41" t="s">
         <v>1164</v>
       </c>
-      <c r="I65" s="99">
+      <c r="I65" s="89">
         <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="51">
-      <c r="A66" s="84"/>
-      <c r="B66" s="84"/>
+      <c r="A66" s="90"/>
+      <c r="B66" s="90"/>
       <c r="C66" s="41" t="s">
         <v>1030</v>
       </c>
@@ -27316,11 +27299,11 @@
       <c r="H66" s="41" t="s">
         <v>1168</v>
       </c>
-      <c r="I66" s="84"/>
+      <c r="I66" s="90"/>
     </row>
     <row r="67" spans="1:9" ht="51">
-      <c r="A67" s="84"/>
-      <c r="B67" s="84"/>
+      <c r="A67" s="90"/>
+      <c r="B67" s="90"/>
       <c r="C67" s="43" t="s">
         <v>1036</v>
       </c>
@@ -27339,72 +27322,72 @@
       <c r="H67" s="41" t="s">
         <v>1172</v>
       </c>
-      <c r="I67" s="93"/>
+      <c r="I67" s="84"/>
     </row>
     <row r="68" spans="1:9" ht="12.75">
-      <c r="A68" s="84"/>
-      <c r="B68" s="84"/>
+      <c r="A68" s="90"/>
+      <c r="B68" s="90"/>
       <c r="C68" s="43" t="s">
         <v>1042</v>
       </c>
       <c r="D68" s="41" t="s">
         <v>1043</v>
       </c>
-      <c r="E68" s="91" t="s">
+      <c r="E68" s="83" t="s">
         <v>1107</v>
       </c>
-      <c r="F68" s="93"/>
-      <c r="G68" s="100" t="s">
+      <c r="F68" s="84"/>
+      <c r="G68" s="91" t="s">
         <v>1152</v>
       </c>
-      <c r="H68" s="101"/>
+      <c r="H68" s="92"/>
       <c r="I68" s="43">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="25.5">
-      <c r="A69" s="84"/>
-      <c r="B69" s="84"/>
+      <c r="A69" s="90"/>
+      <c r="B69" s="90"/>
       <c r="C69" s="43" t="s">
         <v>1042</v>
       </c>
-      <c r="D69" s="91" t="s">
+      <c r="D69" s="83" t="s">
         <v>1173</v>
       </c>
-      <c r="E69" s="93"/>
-      <c r="F69" s="91" t="s">
+      <c r="E69" s="84"/>
+      <c r="F69" s="83" t="s">
         <v>1174</v>
       </c>
-      <c r="G69" s="93"/>
+      <c r="G69" s="84"/>
       <c r="H69" s="41" t="s">
         <v>1175</v>
       </c>
-      <c r="I69" s="99">
+      <c r="I69" s="89">
         <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="25.5">
-      <c r="A70" s="84"/>
-      <c r="B70" s="84"/>
+      <c r="A70" s="90"/>
+      <c r="B70" s="90"/>
       <c r="C70" s="43" t="s">
         <v>1049</v>
       </c>
-      <c r="D70" s="91" t="s">
+      <c r="D70" s="83" t="s">
         <v>1176</v>
       </c>
-      <c r="E70" s="93"/>
-      <c r="F70" s="91" t="s">
+      <c r="E70" s="84"/>
+      <c r="F70" s="83" t="s">
         <v>1177</v>
       </c>
-      <c r="G70" s="93"/>
+      <c r="G70" s="84"/>
       <c r="H70" s="41" t="s">
         <v>1178</v>
       </c>
-      <c r="I70" s="93"/>
+      <c r="I70" s="84"/>
     </row>
     <row r="71" spans="1:9" ht="12.75">
-      <c r="A71" s="84"/>
-      <c r="B71" s="84"/>
+      <c r="A71" s="90"/>
+      <c r="B71" s="90"/>
       <c r="C71" s="41" t="s">
         <v>1053</v>
       </c>
@@ -27414,10 +27397,10 @@
       <c r="E71" s="41" t="s">
         <v>1054</v>
       </c>
-      <c r="F71" s="91" t="s">
+      <c r="F71" s="83" t="s">
         <v>1055</v>
       </c>
-      <c r="G71" s="93"/>
+      <c r="G71" s="84"/>
       <c r="H71" s="41" t="s">
         <v>1056</v>
       </c>
@@ -27426,84 +27409,84 @@
       </c>
     </row>
     <row r="72" spans="1:9" ht="12.75">
-      <c r="A72" s="84"/>
-      <c r="B72" s="84"/>
+      <c r="A72" s="90"/>
+      <c r="B72" s="90"/>
       <c r="C72" s="41" t="s">
         <v>1057</v>
       </c>
       <c r="D72" s="41" t="s">
         <v>1043</v>
       </c>
-      <c r="E72" s="91" t="s">
+      <c r="E72" s="83" t="s">
         <v>1179</v>
       </c>
-      <c r="F72" s="92"/>
-      <c r="G72" s="92"/>
-      <c r="H72" s="93"/>
+      <c r="F72" s="85"/>
+      <c r="G72" s="85"/>
+      <c r="H72" s="84"/>
       <c r="I72" s="43">
         <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="12.75">
-      <c r="A73" s="84"/>
-      <c r="B73" s="84"/>
+      <c r="A73" s="90"/>
+      <c r="B73" s="90"/>
       <c r="C73" s="41" t="s">
         <v>1059</v>
       </c>
       <c r="D73" s="41" t="s">
         <v>1043</v>
       </c>
-      <c r="E73" s="91" t="s">
+      <c r="E73" s="83" t="s">
         <v>1060</v>
       </c>
-      <c r="F73" s="92"/>
-      <c r="G73" s="92"/>
-      <c r="H73" s="93"/>
+      <c r="F73" s="85"/>
+      <c r="G73" s="85"/>
+      <c r="H73" s="84"/>
       <c r="I73" s="43">
         <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="12.75">
-      <c r="A74" s="84"/>
-      <c r="B74" s="84"/>
+      <c r="A74" s="90"/>
+      <c r="B74" s="90"/>
       <c r="C74" s="41" t="s">
         <v>1061</v>
       </c>
-      <c r="D74" s="91" t="s">
+      <c r="D74" s="83" t="s">
         <v>1180</v>
       </c>
-      <c r="E74" s="92"/>
-      <c r="F74" s="92"/>
-      <c r="G74" s="92"/>
-      <c r="H74" s="93"/>
+      <c r="E74" s="85"/>
+      <c r="F74" s="85"/>
+      <c r="G74" s="85"/>
+      <c r="H74" s="84"/>
       <c r="I74" s="43">
         <v>2</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="12.75">
-      <c r="A75" s="85"/>
-      <c r="B75" s="85"/>
+      <c r="A75" s="87"/>
+      <c r="B75" s="87"/>
       <c r="C75" s="44" t="s">
         <v>1063</v>
       </c>
-      <c r="D75" s="97" t="s">
+      <c r="D75" s="86" t="s">
         <v>1043</v>
       </c>
-      <c r="E75" s="85"/>
-      <c r="F75" s="97" t="s">
+      <c r="E75" s="87"/>
+      <c r="F75" s="86" t="s">
         <v>1181</v>
       </c>
-      <c r="G75" s="98"/>
-      <c r="H75" s="85"/>
+      <c r="G75" s="88"/>
+      <c r="H75" s="87"/>
       <c r="I75" s="45">
         <v>2</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="12.75">
-      <c r="A76" s="83" t="s">
+      <c r="A76" s="112" t="s">
         <v>905</v>
       </c>
-      <c r="B76" s="83" t="s">
+      <c r="B76" s="112" t="s">
         <v>980</v>
       </c>
       <c r="C76" s="39" t="s">
@@ -27529,8 +27512,8 @@
       </c>
     </row>
     <row r="77" spans="1:9" ht="51">
-      <c r="A77" s="84"/>
-      <c r="B77" s="84"/>
+      <c r="A77" s="90"/>
+      <c r="B77" s="90"/>
       <c r="C77" s="41" t="s">
         <v>1024</v>
       </c>
@@ -27549,13 +27532,13 @@
       <c r="H77" s="41" t="s">
         <v>1186</v>
       </c>
-      <c r="I77" s="99">
+      <c r="I77" s="89">
         <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="51">
-      <c r="A78" s="84"/>
-      <c r="B78" s="84"/>
+      <c r="A78" s="90"/>
+      <c r="B78" s="90"/>
       <c r="C78" s="41" t="s">
         <v>1030</v>
       </c>
@@ -27574,11 +27557,11 @@
       <c r="H78" s="41" t="s">
         <v>1191</v>
       </c>
-      <c r="I78" s="84"/>
+      <c r="I78" s="90"/>
     </row>
     <row r="79" spans="1:9" ht="51">
-      <c r="A79" s="84"/>
-      <c r="B79" s="84"/>
+      <c r="A79" s="90"/>
+      <c r="B79" s="90"/>
       <c r="C79" s="43" t="s">
         <v>1036</v>
       </c>
@@ -27597,72 +27580,72 @@
       <c r="H79" s="41" t="s">
         <v>1196</v>
       </c>
-      <c r="I79" s="93"/>
+      <c r="I79" s="84"/>
     </row>
     <row r="80" spans="1:9" ht="12.75">
-      <c r="A80" s="84"/>
-      <c r="B80" s="84"/>
+      <c r="A80" s="90"/>
+      <c r="B80" s="90"/>
       <c r="C80" s="43" t="s">
         <v>1042</v>
       </c>
       <c r="D80" s="41" t="s">
         <v>1043</v>
       </c>
-      <c r="E80" s="91" t="s">
+      <c r="E80" s="83" t="s">
         <v>1129</v>
       </c>
-      <c r="F80" s="93"/>
-      <c r="G80" s="100" t="s">
+      <c r="F80" s="84"/>
+      <c r="G80" s="91" t="s">
         <v>1197</v>
       </c>
-      <c r="H80" s="101"/>
+      <c r="H80" s="92"/>
       <c r="I80" s="43">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="25.5">
-      <c r="A81" s="84"/>
-      <c r="B81" s="84"/>
+      <c r="A81" s="90"/>
+      <c r="B81" s="90"/>
       <c r="C81" s="43" t="s">
         <v>1042</v>
       </c>
-      <c r="D81" s="91" t="s">
+      <c r="D81" s="83" t="s">
         <v>1198</v>
       </c>
-      <c r="E81" s="93"/>
-      <c r="F81" s="91" t="s">
+      <c r="E81" s="84"/>
+      <c r="F81" s="83" t="s">
         <v>1199</v>
       </c>
-      <c r="G81" s="93"/>
+      <c r="G81" s="84"/>
       <c r="H81" s="41" t="s">
         <v>1200</v>
       </c>
-      <c r="I81" s="99">
+      <c r="I81" s="89">
         <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="25.5">
-      <c r="A82" s="84"/>
-      <c r="B82" s="84"/>
+      <c r="A82" s="90"/>
+      <c r="B82" s="90"/>
       <c r="C82" s="43" t="s">
         <v>1049</v>
       </c>
-      <c r="D82" s="91" t="s">
+      <c r="D82" s="83" t="s">
         <v>1201</v>
       </c>
-      <c r="E82" s="93"/>
-      <c r="F82" s="91" t="s">
+      <c r="E82" s="84"/>
+      <c r="F82" s="83" t="s">
         <v>1202</v>
       </c>
-      <c r="G82" s="93"/>
+      <c r="G82" s="84"/>
       <c r="H82" s="41" t="s">
         <v>1203</v>
       </c>
-      <c r="I82" s="93"/>
+      <c r="I82" s="84"/>
     </row>
     <row r="83" spans="1:9" ht="12.75">
-      <c r="A83" s="84"/>
-      <c r="B83" s="84"/>
+      <c r="A83" s="90"/>
+      <c r="B83" s="90"/>
       <c r="C83" s="41" t="s">
         <v>1053</v>
       </c>
@@ -27672,10 +27655,10 @@
       <c r="E83" s="41" t="s">
         <v>1054</v>
       </c>
-      <c r="F83" s="91" t="s">
+      <c r="F83" s="83" t="s">
         <v>1055</v>
       </c>
-      <c r="G83" s="93"/>
+      <c r="G83" s="84"/>
       <c r="H83" s="41" t="s">
         <v>1056</v>
       </c>
@@ -27684,84 +27667,84 @@
       </c>
     </row>
     <row r="84" spans="1:9" ht="12.75">
-      <c r="A84" s="84"/>
-      <c r="B84" s="84"/>
+      <c r="A84" s="90"/>
+      <c r="B84" s="90"/>
       <c r="C84" s="41" t="s">
         <v>1057</v>
       </c>
       <c r="D84" s="41" t="s">
         <v>1043</v>
       </c>
-      <c r="E84" s="91" t="s">
+      <c r="E84" s="83" t="s">
         <v>1204</v>
       </c>
-      <c r="F84" s="92"/>
-      <c r="G84" s="92"/>
-      <c r="H84" s="93"/>
+      <c r="F84" s="85"/>
+      <c r="G84" s="85"/>
+      <c r="H84" s="84"/>
       <c r="I84" s="43">
         <v>2</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="12.75">
-      <c r="A85" s="84"/>
-      <c r="B85" s="84"/>
+      <c r="A85" s="90"/>
+      <c r="B85" s="90"/>
       <c r="C85" s="41" t="s">
         <v>1059</v>
       </c>
       <c r="D85" s="41" t="s">
         <v>1043</v>
       </c>
-      <c r="E85" s="91" t="s">
+      <c r="E85" s="83" t="s">
         <v>1089</v>
       </c>
-      <c r="F85" s="92"/>
-      <c r="G85" s="92"/>
-      <c r="H85" s="93"/>
+      <c r="F85" s="85"/>
+      <c r="G85" s="85"/>
+      <c r="H85" s="84"/>
       <c r="I85" s="43">
         <v>3</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="12.75">
-      <c r="A86" s="84"/>
-      <c r="B86" s="84"/>
+      <c r="A86" s="90"/>
+      <c r="B86" s="90"/>
       <c r="C86" s="41" t="s">
         <v>1061</v>
       </c>
-      <c r="D86" s="91" t="s">
+      <c r="D86" s="83" t="s">
         <v>1205</v>
       </c>
-      <c r="E86" s="92"/>
-      <c r="F86" s="92"/>
-      <c r="G86" s="92"/>
-      <c r="H86" s="93"/>
+      <c r="E86" s="85"/>
+      <c r="F86" s="85"/>
+      <c r="G86" s="85"/>
+      <c r="H86" s="84"/>
       <c r="I86" s="43">
         <v>2</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="12.75">
-      <c r="A87" s="85"/>
-      <c r="B87" s="85"/>
+      <c r="A87" s="87"/>
+      <c r="B87" s="87"/>
       <c r="C87" s="44" t="s">
         <v>1063</v>
       </c>
-      <c r="D87" s="97" t="s">
+      <c r="D87" s="86" t="s">
         <v>1043</v>
       </c>
-      <c r="E87" s="85"/>
-      <c r="F87" s="97" t="s">
+      <c r="E87" s="87"/>
+      <c r="F87" s="86" t="s">
         <v>1206</v>
       </c>
-      <c r="G87" s="98"/>
-      <c r="H87" s="85"/>
+      <c r="G87" s="88"/>
+      <c r="H87" s="87"/>
       <c r="I87" s="45">
         <v>2</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="12.75">
-      <c r="A88" s="83" t="s">
+      <c r="A88" s="112" t="s">
         <v>902</v>
       </c>
-      <c r="B88" s="83" t="s">
+      <c r="B88" s="112" t="s">
         <v>981</v>
       </c>
       <c r="C88" s="39" t="s">
@@ -27787,8 +27770,8 @@
       </c>
     </row>
     <row r="89" spans="1:9" ht="51">
-      <c r="A89" s="84"/>
-      <c r="B89" s="84"/>
+      <c r="A89" s="90"/>
+      <c r="B89" s="90"/>
       <c r="C89" s="41" t="s">
         <v>1024</v>
       </c>
@@ -27807,13 +27790,13 @@
       <c r="H89" s="41" t="s">
         <v>1210</v>
       </c>
-      <c r="I89" s="99">
+      <c r="I89" s="89">
         <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="51">
-      <c r="A90" s="84"/>
-      <c r="B90" s="84"/>
+      <c r="A90" s="90"/>
+      <c r="B90" s="90"/>
       <c r="C90" s="41" t="s">
         <v>1030</v>
       </c>
@@ -27832,11 +27815,11 @@
       <c r="H90" s="41" t="s">
         <v>1214</v>
       </c>
-      <c r="I90" s="84"/>
+      <c r="I90" s="90"/>
     </row>
     <row r="91" spans="1:9" ht="51">
-      <c r="A91" s="84"/>
-      <c r="B91" s="84"/>
+      <c r="A91" s="90"/>
+      <c r="B91" s="90"/>
       <c r="C91" s="43" t="s">
         <v>1036</v>
       </c>
@@ -27855,72 +27838,72 @@
       <c r="H91" s="41" t="s">
         <v>1218</v>
       </c>
-      <c r="I91" s="93"/>
+      <c r="I91" s="84"/>
     </row>
     <row r="92" spans="1:9" ht="12.75">
-      <c r="A92" s="84"/>
-      <c r="B92" s="84"/>
+      <c r="A92" s="90"/>
+      <c r="B92" s="90"/>
       <c r="C92" s="43" t="s">
         <v>1042</v>
       </c>
       <c r="D92" s="41" t="s">
         <v>1043</v>
       </c>
-      <c r="E92" s="91" t="s">
+      <c r="E92" s="83" t="s">
         <v>1044</v>
       </c>
-      <c r="F92" s="93"/>
-      <c r="G92" s="100" t="s">
+      <c r="F92" s="84"/>
+      <c r="G92" s="91" t="s">
         <v>1197</v>
       </c>
-      <c r="H92" s="101"/>
+      <c r="H92" s="92"/>
       <c r="I92" s="43">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="25.5">
-      <c r="A93" s="84"/>
-      <c r="B93" s="84"/>
+      <c r="A93" s="90"/>
+      <c r="B93" s="90"/>
       <c r="C93" s="43" t="s">
         <v>1042</v>
       </c>
-      <c r="D93" s="91" t="s">
+      <c r="D93" s="83" t="s">
         <v>1219</v>
       </c>
-      <c r="E93" s="93"/>
-      <c r="F93" s="91" t="s">
+      <c r="E93" s="84"/>
+      <c r="F93" s="83" t="s">
         <v>1220</v>
       </c>
-      <c r="G93" s="93"/>
+      <c r="G93" s="84"/>
       <c r="H93" s="41" t="s">
         <v>1221</v>
       </c>
-      <c r="I93" s="99">
+      <c r="I93" s="89">
         <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="25.5">
-      <c r="A94" s="84"/>
-      <c r="B94" s="84"/>
+      <c r="A94" s="90"/>
+      <c r="B94" s="90"/>
       <c r="C94" s="43" t="s">
         <v>1049</v>
       </c>
-      <c r="D94" s="91" t="s">
+      <c r="D94" s="83" t="s">
         <v>1222</v>
       </c>
-      <c r="E94" s="93"/>
-      <c r="F94" s="91" t="s">
+      <c r="E94" s="84"/>
+      <c r="F94" s="83" t="s">
         <v>1223</v>
       </c>
-      <c r="G94" s="93"/>
+      <c r="G94" s="84"/>
       <c r="H94" s="41" t="s">
         <v>1224</v>
       </c>
-      <c r="I94" s="93"/>
+      <c r="I94" s="84"/>
     </row>
     <row r="95" spans="1:9" ht="12.75">
-      <c r="A95" s="84"/>
-      <c r="B95" s="84"/>
+      <c r="A95" s="90"/>
+      <c r="B95" s="90"/>
       <c r="C95" s="41" t="s">
         <v>1053</v>
       </c>
@@ -27930,10 +27913,10 @@
       <c r="E95" s="41" t="s">
         <v>1054</v>
       </c>
-      <c r="F95" s="91" t="s">
+      <c r="F95" s="83" t="s">
         <v>1055</v>
       </c>
-      <c r="G95" s="93"/>
+      <c r="G95" s="84"/>
       <c r="H95" s="41" t="s">
         <v>1056</v>
       </c>
@@ -27942,84 +27925,84 @@
       </c>
     </row>
     <row r="96" spans="1:9" ht="12.75">
-      <c r="A96" s="84"/>
-      <c r="B96" s="84"/>
+      <c r="A96" s="90"/>
+      <c r="B96" s="90"/>
       <c r="C96" s="41" t="s">
         <v>1057</v>
       </c>
       <c r="D96" s="41" t="s">
         <v>1043</v>
       </c>
-      <c r="E96" s="91" t="s">
+      <c r="E96" s="83" t="s">
         <v>1225</v>
       </c>
-      <c r="F96" s="92"/>
-      <c r="G96" s="92"/>
-      <c r="H96" s="93"/>
+      <c r="F96" s="85"/>
+      <c r="G96" s="85"/>
+      <c r="H96" s="84"/>
       <c r="I96" s="43">
         <v>2</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="12.75">
-      <c r="A97" s="84"/>
-      <c r="B97" s="84"/>
+      <c r="A97" s="90"/>
+      <c r="B97" s="90"/>
       <c r="C97" s="41" t="s">
         <v>1059</v>
       </c>
       <c r="D97" s="41" t="s">
         <v>1043</v>
       </c>
-      <c r="E97" s="91" t="s">
+      <c r="E97" s="83" t="s">
         <v>1089</v>
       </c>
-      <c r="F97" s="92"/>
-      <c r="G97" s="92"/>
-      <c r="H97" s="93"/>
+      <c r="F97" s="85"/>
+      <c r="G97" s="85"/>
+      <c r="H97" s="84"/>
       <c r="I97" s="43">
         <v>3</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="12.75">
-      <c r="A98" s="84"/>
-      <c r="B98" s="84"/>
+      <c r="A98" s="90"/>
+      <c r="B98" s="90"/>
       <c r="C98" s="41" t="s">
         <v>1061</v>
       </c>
-      <c r="D98" s="91" t="s">
+      <c r="D98" s="83" t="s">
         <v>1226</v>
       </c>
-      <c r="E98" s="92"/>
-      <c r="F98" s="92"/>
-      <c r="G98" s="92"/>
-      <c r="H98" s="93"/>
+      <c r="E98" s="85"/>
+      <c r="F98" s="85"/>
+      <c r="G98" s="85"/>
+      <c r="H98" s="84"/>
       <c r="I98" s="43">
         <v>2</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="12.75">
-      <c r="A99" s="85"/>
-      <c r="B99" s="85"/>
+      <c r="A99" s="87"/>
+      <c r="B99" s="87"/>
       <c r="C99" s="46" t="s">
         <v>1063</v>
       </c>
-      <c r="D99" s="108" t="s">
+      <c r="D99" s="109" t="s">
         <v>1043</v>
       </c>
-      <c r="E99" s="84"/>
-      <c r="F99" s="108" t="s">
+      <c r="E99" s="90"/>
+      <c r="F99" s="109" t="s">
         <v>1227</v>
       </c>
-      <c r="G99" s="109"/>
-      <c r="H99" s="84"/>
+      <c r="G99" s="94"/>
+      <c r="H99" s="90"/>
       <c r="I99" s="42">
         <v>2</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="38.25">
-      <c r="A100" s="86" t="s">
+      <c r="A100" s="116" t="s">
         <v>982</v>
       </c>
-      <c r="B100" s="86" t="s">
+      <c r="B100" s="116" t="s">
         <v>1228</v>
       </c>
       <c r="C100" s="47" t="s">
@@ -28045,8 +28028,8 @@
       </c>
     </row>
     <row r="101" spans="1:9" ht="38.25">
-      <c r="A101" s="87"/>
-      <c r="B101" s="87"/>
+      <c r="A101" s="96"/>
+      <c r="B101" s="96"/>
       <c r="C101" s="49" t="s">
         <v>1024</v>
       </c>
@@ -28065,11 +28048,11 @@
       <c r="H101" s="36" t="s">
         <v>1233</v>
       </c>
-      <c r="I101" s="87"/>
+      <c r="I101" s="96"/>
     </row>
     <row r="102" spans="1:9" ht="38.25">
-      <c r="A102" s="87"/>
-      <c r="B102" s="87"/>
+      <c r="A102" s="96"/>
+      <c r="B102" s="96"/>
       <c r="C102" s="49" t="s">
         <v>1030</v>
       </c>
@@ -28088,11 +28071,11 @@
       <c r="H102" s="36" t="s">
         <v>1238</v>
       </c>
-      <c r="I102" s="87"/>
+      <c r="I102" s="96"/>
     </row>
     <row r="103" spans="1:9" ht="38.25">
-      <c r="A103" s="87"/>
-      <c r="B103" s="87"/>
+      <c r="A103" s="96"/>
+      <c r="B103" s="96"/>
       <c r="C103" s="50" t="s">
         <v>1036</v>
       </c>
@@ -28111,11 +28094,11 @@
       <c r="H103" s="36" t="s">
         <v>1243</v>
       </c>
-      <c r="I103" s="87"/>
+      <c r="I103" s="96"/>
     </row>
     <row r="104" spans="1:9" ht="38.25">
-      <c r="A104" s="88"/>
-      <c r="B104" s="88"/>
+      <c r="A104" s="108"/>
+      <c r="B104" s="108"/>
       <c r="C104" s="51" t="s">
         <v>1042</v>
       </c>
@@ -28134,13 +28117,13 @@
       <c r="H104" s="52" t="s">
         <v>1248</v>
       </c>
-      <c r="I104" s="88"/>
+      <c r="I104" s="108"/>
     </row>
     <row r="105" spans="1:9" ht="204">
-      <c r="A105" s="86" t="s">
+      <c r="A105" s="116" t="s">
         <v>985</v>
       </c>
-      <c r="B105" s="86" t="s">
+      <c r="B105" s="116" t="s">
         <v>1228</v>
       </c>
       <c r="C105" s="47" t="s">
@@ -28166,8 +28149,8 @@
       </c>
     </row>
     <row r="106" spans="1:9" ht="204">
-      <c r="A106" s="87"/>
-      <c r="B106" s="87"/>
+      <c r="A106" s="96"/>
+      <c r="B106" s="96"/>
       <c r="C106" s="49" t="s">
         <v>1024</v>
       </c>
@@ -28186,11 +28169,11 @@
       <c r="H106" s="48" t="s">
         <v>1253</v>
       </c>
-      <c r="I106" s="87"/>
+      <c r="I106" s="96"/>
     </row>
     <row r="107" spans="1:9" ht="204">
-      <c r="A107" s="87"/>
-      <c r="B107" s="87"/>
+      <c r="A107" s="96"/>
+      <c r="B107" s="96"/>
       <c r="C107" s="49" t="s">
         <v>1030</v>
       </c>
@@ -28209,11 +28192,11 @@
       <c r="H107" s="48" t="s">
         <v>1258</v>
       </c>
-      <c r="I107" s="87"/>
+      <c r="I107" s="96"/>
     </row>
     <row r="108" spans="1:9" ht="204">
-      <c r="A108" s="87"/>
-      <c r="B108" s="87"/>
+      <c r="A108" s="96"/>
+      <c r="B108" s="96"/>
       <c r="C108" s="50" t="s">
         <v>1036</v>
       </c>
@@ -28232,11 +28215,11 @@
       <c r="H108" s="48" t="s">
         <v>1263</v>
       </c>
-      <c r="I108" s="87"/>
+      <c r="I108" s="96"/>
     </row>
     <row r="109" spans="1:9" ht="204">
-      <c r="A109" s="88"/>
-      <c r="B109" s="88"/>
+      <c r="A109" s="108"/>
+      <c r="B109" s="108"/>
       <c r="C109" s="53" t="s">
         <v>1042</v>
       </c>
@@ -28255,13 +28238,13 @@
       <c r="H109" s="54" t="s">
         <v>1268</v>
       </c>
-      <c r="I109" s="88"/>
+      <c r="I109" s="108"/>
     </row>
     <row r="110" spans="1:9" ht="25.5">
-      <c r="A110" s="86" t="s">
+      <c r="A110" s="116" t="s">
         <v>987</v>
       </c>
-      <c r="B110" s="86" t="s">
+      <c r="B110" s="116" t="s">
         <v>1228</v>
       </c>
       <c r="C110" s="47" t="s">
@@ -28270,10 +28253,10 @@
       <c r="D110" s="48" t="s">
         <v>1043</v>
       </c>
-      <c r="E110" s="102" t="s">
+      <c r="E110" s="105" t="s">
         <v>1269</v>
       </c>
-      <c r="F110" s="103"/>
+      <c r="F110" s="106"/>
       <c r="G110" s="48" t="s">
         <v>1270</v>
       </c>
@@ -28285,113 +28268,113 @@
       </c>
     </row>
     <row r="111" spans="1:9" ht="25.5">
-      <c r="A111" s="87"/>
-      <c r="B111" s="87"/>
+      <c r="A111" s="96"/>
+      <c r="B111" s="96"/>
       <c r="C111" s="49" t="s">
         <v>1024</v>
       </c>
       <c r="D111" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E111" s="100" t="s">
+      <c r="E111" s="91" t="s">
         <v>1269</v>
       </c>
-      <c r="F111" s="101"/>
+      <c r="F111" s="92"/>
       <c r="G111" s="36" t="s">
         <v>1270</v>
       </c>
       <c r="H111" s="36" t="s">
         <v>1271</v>
       </c>
-      <c r="I111" s="87"/>
+      <c r="I111" s="96"/>
     </row>
     <row r="112" spans="1:9" ht="25.5">
-      <c r="A112" s="87"/>
-      <c r="B112" s="87"/>
+      <c r="A112" s="96"/>
+      <c r="B112" s="96"/>
       <c r="C112" s="49" t="s">
         <v>1030</v>
       </c>
       <c r="D112" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E112" s="100" t="s">
+      <c r="E112" s="91" t="s">
         <v>1269</v>
       </c>
-      <c r="F112" s="101"/>
+      <c r="F112" s="92"/>
       <c r="G112" s="36" t="s">
         <v>1270</v>
       </c>
       <c r="H112" s="36" t="s">
         <v>1271</v>
       </c>
-      <c r="I112" s="87"/>
+      <c r="I112" s="96"/>
     </row>
     <row r="113" spans="1:9" ht="25.5">
-      <c r="A113" s="87"/>
-      <c r="B113" s="87"/>
+      <c r="A113" s="96"/>
+      <c r="B113" s="96"/>
       <c r="C113" s="50" t="s">
         <v>1036</v>
       </c>
       <c r="D113" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E113" s="100" t="s">
+      <c r="E113" s="91" t="s">
         <v>1272</v>
       </c>
-      <c r="F113" s="101"/>
+      <c r="F113" s="92"/>
       <c r="G113" s="36" t="s">
         <v>1273</v>
       </c>
       <c r="H113" s="36" t="s">
         <v>1274</v>
       </c>
-      <c r="I113" s="87"/>
+      <c r="I113" s="96"/>
     </row>
     <row r="114" spans="1:9" ht="25.5">
-      <c r="A114" s="87"/>
-      <c r="B114" s="87"/>
+      <c r="A114" s="96"/>
+      <c r="B114" s="96"/>
       <c r="C114" s="50" t="s">
         <v>1042</v>
       </c>
       <c r="D114" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E114" s="100" t="s">
+      <c r="E114" s="91" t="s">
         <v>1275</v>
       </c>
-      <c r="F114" s="101"/>
+      <c r="F114" s="92"/>
       <c r="G114" s="36" t="s">
         <v>1276</v>
       </c>
       <c r="H114" s="36" t="s">
         <v>1277</v>
       </c>
-      <c r="I114" s="87"/>
+      <c r="I114" s="96"/>
     </row>
     <row r="115" spans="1:9" ht="25.5">
-      <c r="A115" s="87"/>
-      <c r="B115" s="87"/>
+      <c r="A115" s="96"/>
+      <c r="B115" s="96"/>
       <c r="C115" s="50" t="s">
         <v>1049</v>
       </c>
       <c r="D115" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E115" s="112" t="s">
+      <c r="E115" s="102" t="s">
         <v>1278</v>
       </c>
-      <c r="F115" s="101"/>
+      <c r="F115" s="92"/>
       <c r="G115" s="55" t="s">
         <v>1279</v>
       </c>
       <c r="H115" s="55" t="s">
         <v>1280</v>
       </c>
-      <c r="I115" s="87"/>
+      <c r="I115" s="96"/>
     </row>
     <row r="116" spans="1:9" ht="25.5">
-      <c r="A116" s="88"/>
-      <c r="B116" s="88"/>
+      <c r="A116" s="108"/>
+      <c r="B116" s="108"/>
       <c r="C116" s="56" t="s">
         <v>1053</v>
       </c>
@@ -28408,13 +28391,13 @@
       <c r="H116" s="52" t="s">
         <v>1283</v>
       </c>
-      <c r="I116" s="88"/>
+      <c r="I116" s="108"/>
     </row>
     <row r="117" spans="1:9" ht="25.5">
-      <c r="A117" s="86" t="s">
+      <c r="A117" s="116" t="s">
         <v>989</v>
       </c>
-      <c r="B117" s="86" t="s">
+      <c r="B117" s="116" t="s">
         <v>1228</v>
       </c>
       <c r="C117" s="47" t="s">
@@ -28423,10 +28406,10 @@
       <c r="D117" s="48" t="s">
         <v>1043</v>
       </c>
-      <c r="E117" s="102" t="s">
+      <c r="E117" s="105" t="s">
         <v>1284</v>
       </c>
-      <c r="F117" s="103"/>
+      <c r="F117" s="106"/>
       <c r="G117" s="48" t="s">
         <v>1285</v>
       </c>
@@ -28438,136 +28421,136 @@
       </c>
     </row>
     <row r="118" spans="1:9" ht="25.5">
-      <c r="A118" s="87"/>
-      <c r="B118" s="87"/>
+      <c r="A118" s="96"/>
+      <c r="B118" s="96"/>
       <c r="C118" s="49" t="s">
         <v>1024</v>
       </c>
       <c r="D118" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E118" s="100" t="s">
+      <c r="E118" s="91" t="s">
         <v>1284</v>
       </c>
-      <c r="F118" s="101"/>
+      <c r="F118" s="92"/>
       <c r="G118" s="36" t="s">
         <v>1285</v>
       </c>
       <c r="H118" s="36" t="s">
         <v>1286</v>
       </c>
-      <c r="I118" s="87"/>
+      <c r="I118" s="96"/>
     </row>
     <row r="119" spans="1:9" ht="25.5">
-      <c r="A119" s="87"/>
-      <c r="B119" s="87"/>
+      <c r="A119" s="96"/>
+      <c r="B119" s="96"/>
       <c r="C119" s="49" t="s">
         <v>1030</v>
       </c>
       <c r="D119" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E119" s="100" t="s">
+      <c r="E119" s="91" t="s">
         <v>1284</v>
       </c>
-      <c r="F119" s="101"/>
+      <c r="F119" s="92"/>
       <c r="G119" s="36" t="s">
         <v>1285</v>
       </c>
       <c r="H119" s="36" t="s">
         <v>1286</v>
       </c>
-      <c r="I119" s="87"/>
+      <c r="I119" s="96"/>
     </row>
     <row r="120" spans="1:9" ht="25.5">
-      <c r="A120" s="87"/>
-      <c r="B120" s="87"/>
+      <c r="A120" s="96"/>
+      <c r="B120" s="96"/>
       <c r="C120" s="50" t="s">
         <v>1036</v>
       </c>
       <c r="D120" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E120" s="100" t="s">
+      <c r="E120" s="91" t="s">
         <v>1287</v>
       </c>
-      <c r="F120" s="101"/>
+      <c r="F120" s="92"/>
       <c r="G120" s="36" t="s">
         <v>1288</v>
       </c>
       <c r="H120" s="36" t="s">
         <v>1289</v>
       </c>
-      <c r="I120" s="87"/>
+      <c r="I120" s="96"/>
     </row>
     <row r="121" spans="1:9" ht="25.5">
-      <c r="A121" s="87"/>
-      <c r="B121" s="87"/>
+      <c r="A121" s="96"/>
+      <c r="B121" s="96"/>
       <c r="C121" s="50" t="s">
         <v>1042</v>
       </c>
       <c r="D121" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E121" s="100" t="s">
+      <c r="E121" s="91" t="s">
         <v>1290</v>
       </c>
-      <c r="F121" s="101"/>
+      <c r="F121" s="92"/>
       <c r="G121" s="36" t="s">
         <v>1291</v>
       </c>
       <c r="H121" s="36" t="s">
         <v>1292</v>
       </c>
-      <c r="I121" s="87"/>
+      <c r="I121" s="96"/>
     </row>
     <row r="122" spans="1:9" ht="25.5">
-      <c r="A122" s="87"/>
-      <c r="B122" s="87"/>
+      <c r="A122" s="96"/>
+      <c r="B122" s="96"/>
       <c r="C122" s="50" t="s">
         <v>1049</v>
       </c>
       <c r="D122" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E122" s="112" t="s">
+      <c r="E122" s="102" t="s">
         <v>1293</v>
       </c>
-      <c r="F122" s="101"/>
+      <c r="F122" s="92"/>
       <c r="G122" s="55" t="s">
         <v>1294</v>
       </c>
       <c r="H122" s="55" t="s">
         <v>1295</v>
       </c>
-      <c r="I122" s="87"/>
+      <c r="I122" s="96"/>
     </row>
     <row r="123" spans="1:9" ht="25.5">
-      <c r="A123" s="88"/>
-      <c r="B123" s="88"/>
+      <c r="A123" s="108"/>
+      <c r="B123" s="108"/>
       <c r="C123" s="57" t="s">
         <v>1053</v>
       </c>
       <c r="D123" s="37" t="s">
         <v>1043</v>
       </c>
-      <c r="E123" s="94" t="s">
+      <c r="E123" s="103" t="s">
         <v>1296</v>
       </c>
-      <c r="F123" s="95"/>
+      <c r="F123" s="104"/>
       <c r="G123" s="37" t="s">
         <v>1297</v>
       </c>
       <c r="H123" s="37" t="s">
         <v>1298</v>
       </c>
-      <c r="I123" s="88"/>
+      <c r="I123" s="108"/>
     </row>
     <row r="124" spans="1:9" ht="25.5">
-      <c r="A124" s="89" t="s">
+      <c r="A124" s="113" t="s">
         <v>648</v>
       </c>
-      <c r="B124" s="89" t="s">
+      <c r="B124" s="113" t="s">
         <v>992</v>
       </c>
       <c r="C124" s="58" t="s">
@@ -28593,75 +28576,75 @@
       </c>
     </row>
     <row r="125" spans="1:9" ht="12.75">
-      <c r="A125" s="87"/>
-      <c r="B125" s="87"/>
+      <c r="A125" s="96"/>
+      <c r="B125" s="96"/>
       <c r="C125" s="49" t="s">
         <v>1024</v>
       </c>
       <c r="D125" s="34" t="s">
         <v>1043</v>
       </c>
-      <c r="E125" s="100" t="s">
+      <c r="E125" s="91" t="s">
         <v>1304</v>
       </c>
-      <c r="F125" s="106"/>
-      <c r="G125" s="106"/>
-      <c r="H125" s="101"/>
+      <c r="F125" s="98"/>
+      <c r="G125" s="98"/>
+      <c r="H125" s="92"/>
       <c r="I125" s="50">
         <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="12.75">
-      <c r="A126" s="87"/>
-      <c r="B126" s="87"/>
+      <c r="A126" s="96"/>
+      <c r="B126" s="96"/>
       <c r="C126" s="49" t="s">
         <v>1030</v>
       </c>
       <c r="D126" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E126" s="100" t="s">
+      <c r="E126" s="91" t="s">
         <v>1305</v>
       </c>
-      <c r="F126" s="106"/>
-      <c r="G126" s="106"/>
-      <c r="H126" s="101"/>
+      <c r="F126" s="98"/>
+      <c r="G126" s="98"/>
+      <c r="H126" s="92"/>
       <c r="I126" s="50">
         <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="12.75">
-      <c r="A127" s="87"/>
-      <c r="B127" s="87"/>
+      <c r="A127" s="96"/>
+      <c r="B127" s="96"/>
       <c r="C127" s="50" t="s">
         <v>1036</v>
       </c>
       <c r="D127" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E127" s="100" t="s">
+      <c r="E127" s="91" t="s">
         <v>1306</v>
       </c>
-      <c r="F127" s="106"/>
-      <c r="G127" s="106"/>
-      <c r="H127" s="101"/>
+      <c r="F127" s="98"/>
+      <c r="G127" s="98"/>
+      <c r="H127" s="92"/>
       <c r="I127" s="50">
         <v>2</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="51">
-      <c r="A128" s="87"/>
-      <c r="B128" s="87"/>
+      <c r="A128" s="96"/>
+      <c r="B128" s="96"/>
       <c r="C128" s="50" t="s">
         <v>1042</v>
       </c>
       <c r="D128" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E128" s="100" t="s">
+      <c r="E128" s="91" t="s">
         <v>1307</v>
       </c>
-      <c r="F128" s="101"/>
+      <c r="F128" s="92"/>
       <c r="G128" s="36" t="s">
         <v>1308</v>
       </c>
@@ -28673,8 +28656,8 @@
       </c>
     </row>
     <row r="129" spans="1:9" ht="25.5">
-      <c r="A129" s="90"/>
-      <c r="B129" s="90"/>
+      <c r="A129" s="114"/>
+      <c r="B129" s="114"/>
       <c r="C129" s="61" t="s">
         <v>1049</v>
       </c>
@@ -28698,10 +28681,10 @@
       </c>
     </row>
     <row r="130" spans="1:9" ht="25.5">
-      <c r="A130" s="89" t="s">
+      <c r="A130" s="113" t="s">
         <v>650</v>
       </c>
-      <c r="B130" s="89" t="s">
+      <c r="B130" s="113" t="s">
         <v>993</v>
       </c>
       <c r="C130" s="58" t="s">
@@ -28727,75 +28710,75 @@
       </c>
     </row>
     <row r="131" spans="1:9" ht="12.75">
-      <c r="A131" s="87"/>
-      <c r="B131" s="87"/>
+      <c r="A131" s="96"/>
+      <c r="B131" s="96"/>
       <c r="C131" s="49" t="s">
         <v>1024</v>
       </c>
       <c r="D131" s="34" t="s">
         <v>1043</v>
       </c>
-      <c r="E131" s="100" t="s">
+      <c r="E131" s="91" t="s">
         <v>1314</v>
       </c>
-      <c r="F131" s="106"/>
-      <c r="G131" s="106"/>
-      <c r="H131" s="101"/>
+      <c r="F131" s="98"/>
+      <c r="G131" s="98"/>
+      <c r="H131" s="92"/>
       <c r="I131" s="50">
         <v>1</v>
       </c>
     </row>
     <row r="132" spans="1:9" ht="12.75">
-      <c r="A132" s="87"/>
-      <c r="B132" s="87"/>
+      <c r="A132" s="96"/>
+      <c r="B132" s="96"/>
       <c r="C132" s="49" t="s">
         <v>1030</v>
       </c>
       <c r="D132" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E132" s="100" t="s">
+      <c r="E132" s="91" t="s">
         <v>1305</v>
       </c>
-      <c r="F132" s="106"/>
-      <c r="G132" s="106"/>
-      <c r="H132" s="101"/>
+      <c r="F132" s="98"/>
+      <c r="G132" s="98"/>
+      <c r="H132" s="92"/>
       <c r="I132" s="50">
         <v>1</v>
       </c>
     </row>
     <row r="133" spans="1:9" ht="12.75">
-      <c r="A133" s="87"/>
-      <c r="B133" s="87"/>
+      <c r="A133" s="96"/>
+      <c r="B133" s="96"/>
       <c r="C133" s="50" t="s">
         <v>1036</v>
       </c>
       <c r="D133" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E133" s="100" t="s">
+      <c r="E133" s="91" t="s">
         <v>1306</v>
       </c>
-      <c r="F133" s="106"/>
-      <c r="G133" s="106"/>
-      <c r="H133" s="101"/>
+      <c r="F133" s="98"/>
+      <c r="G133" s="98"/>
+      <c r="H133" s="92"/>
       <c r="I133" s="50">
         <v>2</v>
       </c>
     </row>
     <row r="134" spans="1:9" ht="51">
-      <c r="A134" s="90"/>
-      <c r="B134" s="90"/>
+      <c r="A134" s="114"/>
+      <c r="B134" s="114"/>
       <c r="C134" s="61" t="s">
         <v>1042</v>
       </c>
       <c r="D134" s="62" t="s">
         <v>1043</v>
       </c>
-      <c r="E134" s="104" t="s">
+      <c r="E134" s="100" t="s">
         <v>1307</v>
       </c>
-      <c r="F134" s="105"/>
+      <c r="F134" s="101"/>
       <c r="G134" s="62" t="s">
         <v>1308</v>
       </c>
@@ -28807,10 +28790,10 @@
       </c>
     </row>
     <row r="135" spans="1:9" ht="25.5">
-      <c r="A135" s="89" t="s">
+      <c r="A135" s="113" t="s">
         <v>768</v>
       </c>
-      <c r="B135" s="89" t="s">
+      <c r="B135" s="113" t="s">
         <v>994</v>
       </c>
       <c r="C135" s="58" t="s">
@@ -28836,75 +28819,75 @@
       </c>
     </row>
     <row r="136" spans="1:9" ht="12.75">
-      <c r="A136" s="87"/>
-      <c r="B136" s="87"/>
+      <c r="A136" s="96"/>
+      <c r="B136" s="96"/>
       <c r="C136" s="49" t="s">
         <v>1024</v>
       </c>
       <c r="D136" s="34" t="s">
         <v>1043</v>
       </c>
-      <c r="E136" s="100" t="s">
+      <c r="E136" s="91" t="s">
         <v>1315</v>
       </c>
-      <c r="F136" s="106"/>
-      <c r="G136" s="106"/>
-      <c r="H136" s="101"/>
+      <c r="F136" s="98"/>
+      <c r="G136" s="98"/>
+      <c r="H136" s="92"/>
       <c r="I136" s="50">
         <v>1</v>
       </c>
     </row>
     <row r="137" spans="1:9" ht="12.75">
-      <c r="A137" s="87"/>
-      <c r="B137" s="87"/>
+      <c r="A137" s="96"/>
+      <c r="B137" s="96"/>
       <c r="C137" s="49" t="s">
         <v>1030</v>
       </c>
       <c r="D137" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E137" s="100" t="s">
+      <c r="E137" s="91" t="s">
         <v>1316</v>
       </c>
-      <c r="F137" s="106"/>
-      <c r="G137" s="106"/>
-      <c r="H137" s="101"/>
+      <c r="F137" s="98"/>
+      <c r="G137" s="98"/>
+      <c r="H137" s="92"/>
       <c r="I137" s="50">
         <v>1</v>
       </c>
     </row>
     <row r="138" spans="1:9" ht="12.75">
-      <c r="A138" s="87"/>
-      <c r="B138" s="87"/>
+      <c r="A138" s="96"/>
+      <c r="B138" s="96"/>
       <c r="C138" s="50" t="s">
         <v>1036</v>
       </c>
       <c r="D138" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E138" s="100" t="s">
+      <c r="E138" s="91" t="s">
         <v>1317</v>
       </c>
-      <c r="F138" s="106"/>
-      <c r="G138" s="106"/>
-      <c r="H138" s="101"/>
+      <c r="F138" s="98"/>
+      <c r="G138" s="98"/>
+      <c r="H138" s="92"/>
       <c r="I138" s="50">
         <v>2</v>
       </c>
     </row>
     <row r="139" spans="1:9" ht="51">
-      <c r="A139" s="90"/>
-      <c r="B139" s="90"/>
+      <c r="A139" s="114"/>
+      <c r="B139" s="114"/>
       <c r="C139" s="61" t="s">
         <v>1042</v>
       </c>
       <c r="D139" s="62" t="s">
         <v>1043</v>
       </c>
-      <c r="E139" s="104" t="s">
+      <c r="E139" s="100" t="s">
         <v>1307</v>
       </c>
-      <c r="F139" s="105"/>
+      <c r="F139" s="101"/>
       <c r="G139" s="62" t="s">
         <v>1308</v>
       </c>
@@ -28916,10 +28899,10 @@
       </c>
     </row>
     <row r="140" spans="1:9" ht="25.5">
-      <c r="A140" s="89" t="s">
+      <c r="A140" s="113" t="s">
         <v>774</v>
       </c>
-      <c r="B140" s="89" t="s">
+      <c r="B140" s="113" t="s">
         <v>995</v>
       </c>
       <c r="C140" s="58" t="s">
@@ -28945,75 +28928,75 @@
       </c>
     </row>
     <row r="141" spans="1:9" ht="12.75">
-      <c r="A141" s="87"/>
-      <c r="B141" s="87"/>
+      <c r="A141" s="96"/>
+      <c r="B141" s="96"/>
       <c r="C141" s="49" t="s">
         <v>1024</v>
       </c>
       <c r="D141" s="34" t="s">
         <v>1043</v>
       </c>
-      <c r="E141" s="100" t="s">
+      <c r="E141" s="91" t="s">
         <v>1318</v>
       </c>
-      <c r="F141" s="106"/>
-      <c r="G141" s="106"/>
-      <c r="H141" s="101"/>
+      <c r="F141" s="98"/>
+      <c r="G141" s="98"/>
+      <c r="H141" s="92"/>
       <c r="I141" s="50">
         <v>1</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="12.75">
-      <c r="A142" s="87"/>
-      <c r="B142" s="87"/>
+      <c r="A142" s="96"/>
+      <c r="B142" s="96"/>
       <c r="C142" s="49" t="s">
         <v>1030</v>
       </c>
       <c r="D142" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E142" s="100" t="s">
+      <c r="E142" s="91" t="s">
         <v>1316</v>
       </c>
-      <c r="F142" s="106"/>
-      <c r="G142" s="106"/>
-      <c r="H142" s="101"/>
+      <c r="F142" s="98"/>
+      <c r="G142" s="98"/>
+      <c r="H142" s="92"/>
       <c r="I142" s="50">
         <v>1</v>
       </c>
     </row>
     <row r="143" spans="1:9" ht="12.75">
-      <c r="A143" s="87"/>
-      <c r="B143" s="87"/>
+      <c r="A143" s="96"/>
+      <c r="B143" s="96"/>
       <c r="C143" s="50" t="s">
         <v>1036</v>
       </c>
       <c r="D143" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E143" s="100" t="s">
+      <c r="E143" s="91" t="s">
         <v>1317</v>
       </c>
-      <c r="F143" s="106"/>
-      <c r="G143" s="106"/>
-      <c r="H143" s="101"/>
+      <c r="F143" s="98"/>
+      <c r="G143" s="98"/>
+      <c r="H143" s="92"/>
       <c r="I143" s="50">
         <v>2</v>
       </c>
     </row>
     <row r="144" spans="1:9" ht="51">
-      <c r="A144" s="90"/>
-      <c r="B144" s="90"/>
+      <c r="A144" s="114"/>
+      <c r="B144" s="114"/>
       <c r="C144" s="61" t="s">
         <v>1042</v>
       </c>
       <c r="D144" s="62" t="s">
         <v>1043</v>
       </c>
-      <c r="E144" s="104" t="s">
+      <c r="E144" s="100" t="s">
         <v>1307</v>
       </c>
-      <c r="F144" s="105"/>
+      <c r="F144" s="101"/>
       <c r="G144" s="62" t="s">
         <v>1308</v>
       </c>
@@ -29025,10 +29008,10 @@
       </c>
     </row>
     <row r="145" spans="1:9" ht="25.5">
-      <c r="A145" s="89" t="s">
+      <c r="A145" s="113" t="s">
         <v>786</v>
       </c>
-      <c r="B145" s="89" t="s">
+      <c r="B145" s="113" t="s">
         <v>996</v>
       </c>
       <c r="C145" s="58" t="s">
@@ -29054,75 +29037,75 @@
       </c>
     </row>
     <row r="146" spans="1:9" ht="12.75">
-      <c r="A146" s="87"/>
-      <c r="B146" s="87"/>
+      <c r="A146" s="96"/>
+      <c r="B146" s="96"/>
       <c r="C146" s="49" t="s">
         <v>1024</v>
       </c>
       <c r="D146" s="34" t="s">
         <v>1043</v>
       </c>
-      <c r="E146" s="100" t="s">
+      <c r="E146" s="91" t="s">
         <v>1319</v>
       </c>
-      <c r="F146" s="106"/>
-      <c r="G146" s="106"/>
-      <c r="H146" s="101"/>
+      <c r="F146" s="98"/>
+      <c r="G146" s="98"/>
+      <c r="H146" s="92"/>
       <c r="I146" s="50">
         <v>1</v>
       </c>
     </row>
     <row r="147" spans="1:9" ht="12.75">
-      <c r="A147" s="87"/>
-      <c r="B147" s="87"/>
+      <c r="A147" s="96"/>
+      <c r="B147" s="96"/>
       <c r="C147" s="49" t="s">
         <v>1030</v>
       </c>
       <c r="D147" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E147" s="100" t="s">
+      <c r="E147" s="91" t="s">
         <v>1320</v>
       </c>
-      <c r="F147" s="106"/>
-      <c r="G147" s="106"/>
-      <c r="H147" s="101"/>
+      <c r="F147" s="98"/>
+      <c r="G147" s="98"/>
+      <c r="H147" s="92"/>
       <c r="I147" s="50">
         <v>1</v>
       </c>
     </row>
     <row r="148" spans="1:9" ht="12.75">
-      <c r="A148" s="87"/>
-      <c r="B148" s="87"/>
+      <c r="A148" s="96"/>
+      <c r="B148" s="96"/>
       <c r="C148" s="50" t="s">
         <v>1036</v>
       </c>
       <c r="D148" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E148" s="100" t="s">
+      <c r="E148" s="91" t="s">
         <v>1317</v>
       </c>
-      <c r="F148" s="106"/>
-      <c r="G148" s="106"/>
-      <c r="H148" s="101"/>
+      <c r="F148" s="98"/>
+      <c r="G148" s="98"/>
+      <c r="H148" s="92"/>
       <c r="I148" s="50">
         <v>2</v>
       </c>
     </row>
     <row r="149" spans="1:9" ht="51">
-      <c r="A149" s="90"/>
-      <c r="B149" s="90"/>
+      <c r="A149" s="114"/>
+      <c r="B149" s="114"/>
       <c r="C149" s="61" t="s">
         <v>1042</v>
       </c>
       <c r="D149" s="62" t="s">
         <v>1043</v>
       </c>
-      <c r="E149" s="104" t="s">
+      <c r="E149" s="100" t="s">
         <v>1307</v>
       </c>
-      <c r="F149" s="105"/>
+      <c r="F149" s="101"/>
       <c r="G149" s="62" t="s">
         <v>1308</v>
       </c>
@@ -29134,10 +29117,10 @@
       </c>
     </row>
     <row r="150" spans="1:9" ht="25.5">
-      <c r="A150" s="89" t="s">
+      <c r="A150" s="113" t="s">
         <v>780</v>
       </c>
-      <c r="B150" s="89" t="s">
+      <c r="B150" s="113" t="s">
         <v>997</v>
       </c>
       <c r="C150" s="58" t="s">
@@ -29163,75 +29146,75 @@
       </c>
     </row>
     <row r="151" spans="1:9" ht="12.75">
-      <c r="A151" s="87"/>
-      <c r="B151" s="87"/>
+      <c r="A151" s="96"/>
+      <c r="B151" s="96"/>
       <c r="C151" s="49" t="s">
         <v>1024</v>
       </c>
       <c r="D151" s="34" t="s">
         <v>1043</v>
       </c>
-      <c r="E151" s="100" t="s">
+      <c r="E151" s="91" t="s">
         <v>1321</v>
       </c>
-      <c r="F151" s="106"/>
-      <c r="G151" s="106"/>
-      <c r="H151" s="101"/>
+      <c r="F151" s="98"/>
+      <c r="G151" s="98"/>
+      <c r="H151" s="92"/>
       <c r="I151" s="50">
         <v>1</v>
       </c>
     </row>
     <row r="152" spans="1:9" ht="12.75">
-      <c r="A152" s="87"/>
-      <c r="B152" s="87"/>
+      <c r="A152" s="96"/>
+      <c r="B152" s="96"/>
       <c r="C152" s="49" t="s">
         <v>1030</v>
       </c>
       <c r="D152" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E152" s="100" t="s">
+      <c r="E152" s="91" t="s">
         <v>1320</v>
       </c>
-      <c r="F152" s="106"/>
-      <c r="G152" s="106"/>
-      <c r="H152" s="101"/>
+      <c r="F152" s="98"/>
+      <c r="G152" s="98"/>
+      <c r="H152" s="92"/>
       <c r="I152" s="50">
         <v>1</v>
       </c>
     </row>
     <row r="153" spans="1:9" ht="12.75">
-      <c r="A153" s="87"/>
-      <c r="B153" s="87"/>
+      <c r="A153" s="96"/>
+      <c r="B153" s="96"/>
       <c r="C153" s="50" t="s">
         <v>1036</v>
       </c>
       <c r="D153" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E153" s="100" t="s">
+      <c r="E153" s="91" t="s">
         <v>1317</v>
       </c>
-      <c r="F153" s="106"/>
-      <c r="G153" s="106"/>
-      <c r="H153" s="101"/>
+      <c r="F153" s="98"/>
+      <c r="G153" s="98"/>
+      <c r="H153" s="92"/>
       <c r="I153" s="50">
         <v>2</v>
       </c>
     </row>
     <row r="154" spans="1:9" ht="51">
-      <c r="A154" s="90"/>
-      <c r="B154" s="90"/>
+      <c r="A154" s="114"/>
+      <c r="B154" s="114"/>
       <c r="C154" s="61" t="s">
         <v>1042</v>
       </c>
       <c r="D154" s="62" t="s">
         <v>1043</v>
       </c>
-      <c r="E154" s="104" t="s">
+      <c r="E154" s="100" t="s">
         <v>1307</v>
       </c>
-      <c r="F154" s="105"/>
+      <c r="F154" s="101"/>
       <c r="G154" s="62" t="s">
         <v>1308</v>
       </c>
@@ -29243,10 +29226,10 @@
       </c>
     </row>
     <row r="155" spans="1:9" ht="25.5">
-      <c r="A155" s="89" t="s">
+      <c r="A155" s="113" t="s">
         <v>656</v>
       </c>
-      <c r="B155" s="89" t="s">
+      <c r="B155" s="113" t="s">
         <v>998</v>
       </c>
       <c r="C155" s="58" t="s">
@@ -29272,75 +29255,75 @@
       </c>
     </row>
     <row r="156" spans="1:9" ht="12.75">
-      <c r="A156" s="87"/>
-      <c r="B156" s="87"/>
+      <c r="A156" s="96"/>
+      <c r="B156" s="96"/>
       <c r="C156" s="49" t="s">
         <v>1024</v>
       </c>
       <c r="D156" s="34" t="s">
         <v>1043</v>
       </c>
-      <c r="E156" s="100" t="s">
+      <c r="E156" s="91" t="s">
         <v>1322</v>
       </c>
-      <c r="F156" s="106"/>
-      <c r="G156" s="106"/>
-      <c r="H156" s="101"/>
+      <c r="F156" s="98"/>
+      <c r="G156" s="98"/>
+      <c r="H156" s="92"/>
       <c r="I156" s="50">
         <v>1</v>
       </c>
     </row>
     <row r="157" spans="1:9" ht="12.75">
-      <c r="A157" s="87"/>
-      <c r="B157" s="87"/>
+      <c r="A157" s="96"/>
+      <c r="B157" s="96"/>
       <c r="C157" s="49" t="s">
         <v>1030</v>
       </c>
       <c r="D157" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E157" s="100" t="s">
+      <c r="E157" s="91" t="s">
         <v>1323</v>
       </c>
-      <c r="F157" s="106"/>
-      <c r="G157" s="106"/>
-      <c r="H157" s="101"/>
+      <c r="F157" s="98"/>
+      <c r="G157" s="98"/>
+      <c r="H157" s="92"/>
       <c r="I157" s="50">
         <v>1</v>
       </c>
     </row>
     <row r="158" spans="1:9" ht="12.75">
-      <c r="A158" s="87"/>
-      <c r="B158" s="87"/>
+      <c r="A158" s="96"/>
+      <c r="B158" s="96"/>
       <c r="C158" s="50" t="s">
         <v>1036</v>
       </c>
       <c r="D158" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E158" s="100" t="s">
+      <c r="E158" s="91" t="s">
         <v>1306</v>
       </c>
-      <c r="F158" s="106"/>
-      <c r="G158" s="106"/>
-      <c r="H158" s="101"/>
+      <c r="F158" s="98"/>
+      <c r="G158" s="98"/>
+      <c r="H158" s="92"/>
       <c r="I158" s="50">
         <v>2</v>
       </c>
     </row>
     <row r="159" spans="1:9" ht="51">
-      <c r="A159" s="90"/>
-      <c r="B159" s="90"/>
+      <c r="A159" s="114"/>
+      <c r="B159" s="114"/>
       <c r="C159" s="61" t="s">
         <v>1042</v>
       </c>
       <c r="D159" s="62" t="s">
         <v>1043</v>
       </c>
-      <c r="E159" s="104" t="s">
+      <c r="E159" s="100" t="s">
         <v>1307</v>
       </c>
-      <c r="F159" s="105"/>
+      <c r="F159" s="101"/>
       <c r="G159" s="62" t="s">
         <v>1308</v>
       </c>
@@ -29352,10 +29335,10 @@
       </c>
     </row>
     <row r="160" spans="1:9" ht="25.5">
-      <c r="A160" s="89" t="s">
+      <c r="A160" s="113" t="s">
         <v>658</v>
       </c>
-      <c r="B160" s="89" t="s">
+      <c r="B160" s="113" t="s">
         <v>999</v>
       </c>
       <c r="C160" s="58" t="s">
@@ -29381,8 +29364,8 @@
       </c>
     </row>
     <row r="161" spans="1:9" ht="12.75">
-      <c r="A161" s="87"/>
-      <c r="B161" s="87"/>
+      <c r="A161" s="96"/>
+      <c r="B161" s="96"/>
       <c r="C161" s="49" t="s">
         <v>1024</v>
       </c>
@@ -29390,65 +29373,65 @@
         <v>1043</v>
       </c>
       <c r="F161" s="63"/>
-      <c r="G161" s="100" t="s">
+      <c r="G161" s="91" t="s">
         <v>1324</v>
       </c>
-      <c r="H161" s="101"/>
+      <c r="H161" s="92"/>
       <c r="I161" s="50">
         <v>1</v>
       </c>
     </row>
     <row r="162" spans="1:9" ht="12.75">
-      <c r="A162" s="87"/>
-      <c r="B162" s="87"/>
+      <c r="A162" s="96"/>
+      <c r="B162" s="96"/>
       <c r="C162" s="49" t="s">
         <v>1030</v>
       </c>
       <c r="D162" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E162" s="100" t="s">
+      <c r="E162" s="91" t="s">
         <v>1323</v>
       </c>
-      <c r="F162" s="106"/>
-      <c r="G162" s="106"/>
-      <c r="H162" s="101"/>
+      <c r="F162" s="98"/>
+      <c r="G162" s="98"/>
+      <c r="H162" s="92"/>
       <c r="I162" s="50">
         <v>1</v>
       </c>
     </row>
     <row r="163" spans="1:9" ht="12.75">
-      <c r="A163" s="87"/>
-      <c r="B163" s="87"/>
+      <c r="A163" s="96"/>
+      <c r="B163" s="96"/>
       <c r="C163" s="50" t="s">
         <v>1036</v>
       </c>
       <c r="D163" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E163" s="100" t="s">
+      <c r="E163" s="91" t="s">
         <v>1306</v>
       </c>
-      <c r="F163" s="106"/>
-      <c r="G163" s="106"/>
-      <c r="H163" s="101"/>
+      <c r="F163" s="98"/>
+      <c r="G163" s="98"/>
+      <c r="H163" s="92"/>
       <c r="I163" s="50">
         <v>2</v>
       </c>
     </row>
     <row r="164" spans="1:9" ht="51">
-      <c r="A164" s="90"/>
-      <c r="B164" s="90"/>
+      <c r="A164" s="114"/>
+      <c r="B164" s="114"/>
       <c r="C164" s="61" t="s">
         <v>1042</v>
       </c>
       <c r="D164" s="62" t="s">
         <v>1043</v>
       </c>
-      <c r="E164" s="104" t="s">
+      <c r="E164" s="100" t="s">
         <v>1307</v>
       </c>
-      <c r="F164" s="105"/>
+      <c r="F164" s="101"/>
       <c r="G164" s="62" t="s">
         <v>1308</v>
       </c>
@@ -29460,10 +29443,10 @@
       </c>
     </row>
     <row r="165" spans="1:9" ht="25.5">
-      <c r="A165" s="89" t="s">
+      <c r="A165" s="113" t="s">
         <v>802</v>
       </c>
-      <c r="B165" s="89" t="s">
+      <c r="B165" s="113" t="s">
         <v>1000</v>
       </c>
       <c r="C165" s="58" t="s">
@@ -29489,75 +29472,75 @@
       </c>
     </row>
     <row r="166" spans="1:9" ht="12.75">
-      <c r="A166" s="87"/>
-      <c r="B166" s="87"/>
+      <c r="A166" s="96"/>
+      <c r="B166" s="96"/>
       <c r="C166" s="49" t="s">
         <v>1024</v>
       </c>
       <c r="D166" s="34" t="s">
         <v>1043</v>
       </c>
-      <c r="E166" s="100" t="s">
+      <c r="E166" s="91" t="s">
         <v>1325</v>
       </c>
-      <c r="F166" s="106"/>
-      <c r="G166" s="106"/>
-      <c r="H166" s="101"/>
+      <c r="F166" s="98"/>
+      <c r="G166" s="98"/>
+      <c r="H166" s="92"/>
       <c r="I166" s="50">
         <v>1</v>
       </c>
     </row>
     <row r="167" spans="1:9" ht="12.75">
-      <c r="A167" s="87"/>
-      <c r="B167" s="87"/>
+      <c r="A167" s="96"/>
+      <c r="B167" s="96"/>
       <c r="C167" s="49" t="s">
         <v>1030</v>
       </c>
       <c r="D167" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E167" s="100" t="s">
+      <c r="E167" s="91" t="s">
         <v>1326</v>
       </c>
-      <c r="F167" s="106"/>
-      <c r="G167" s="106"/>
-      <c r="H167" s="101"/>
+      <c r="F167" s="98"/>
+      <c r="G167" s="98"/>
+      <c r="H167" s="92"/>
       <c r="I167" s="50">
         <v>1</v>
       </c>
     </row>
     <row r="168" spans="1:9" ht="12.75">
-      <c r="A168" s="87"/>
-      <c r="B168" s="87"/>
+      <c r="A168" s="96"/>
+      <c r="B168" s="96"/>
       <c r="C168" s="50" t="s">
         <v>1036</v>
       </c>
       <c r="D168" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E168" s="100" t="s">
+      <c r="E168" s="91" t="s">
         <v>1306</v>
       </c>
-      <c r="F168" s="106"/>
-      <c r="G168" s="106"/>
-      <c r="H168" s="101"/>
+      <c r="F168" s="98"/>
+      <c r="G168" s="98"/>
+      <c r="H168" s="92"/>
       <c r="I168" s="50">
         <v>2</v>
       </c>
     </row>
     <row r="169" spans="1:9" ht="51">
-      <c r="A169" s="90"/>
-      <c r="B169" s="90"/>
+      <c r="A169" s="114"/>
+      <c r="B169" s="114"/>
       <c r="C169" s="61" t="s">
         <v>1042</v>
       </c>
       <c r="D169" s="62" t="s">
         <v>1043</v>
       </c>
-      <c r="E169" s="104" t="s">
+      <c r="E169" s="100" t="s">
         <v>1307</v>
       </c>
-      <c r="F169" s="105"/>
+      <c r="F169" s="101"/>
       <c r="G169" s="62" t="s">
         <v>1308</v>
       </c>
@@ -29569,10 +29552,10 @@
       </c>
     </row>
     <row r="170" spans="1:9" ht="25.5">
-      <c r="A170" s="89" t="s">
+      <c r="A170" s="113" t="s">
         <v>1327</v>
       </c>
-      <c r="B170" s="89" t="s">
+      <c r="B170" s="113" t="s">
         <v>1001</v>
       </c>
       <c r="C170" s="58" t="s">
@@ -29598,75 +29581,75 @@
       </c>
     </row>
     <row r="171" spans="1:9" ht="12.75">
-      <c r="A171" s="87"/>
-      <c r="B171" s="87"/>
+      <c r="A171" s="96"/>
+      <c r="B171" s="96"/>
       <c r="C171" s="49" t="s">
         <v>1024</v>
       </c>
       <c r="D171" s="34" t="s">
         <v>1043</v>
       </c>
-      <c r="E171" s="100" t="s">
+      <c r="E171" s="91" t="s">
         <v>1328</v>
       </c>
-      <c r="F171" s="106"/>
-      <c r="G171" s="106"/>
-      <c r="H171" s="101"/>
+      <c r="F171" s="98"/>
+      <c r="G171" s="98"/>
+      <c r="H171" s="92"/>
       <c r="I171" s="50">
         <v>1</v>
       </c>
     </row>
     <row r="172" spans="1:9" ht="12.75">
-      <c r="A172" s="87"/>
-      <c r="B172" s="87"/>
+      <c r="A172" s="96"/>
+      <c r="B172" s="96"/>
       <c r="C172" s="49" t="s">
         <v>1030</v>
       </c>
       <c r="D172" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E172" s="100" t="s">
+      <c r="E172" s="91" t="s">
         <v>1326</v>
       </c>
-      <c r="F172" s="106"/>
-      <c r="G172" s="106"/>
-      <c r="H172" s="101"/>
+      <c r="F172" s="98"/>
+      <c r="G172" s="98"/>
+      <c r="H172" s="92"/>
       <c r="I172" s="50">
         <v>1</v>
       </c>
     </row>
     <row r="173" spans="1:9" ht="12.75">
-      <c r="A173" s="87"/>
-      <c r="B173" s="87"/>
+      <c r="A173" s="96"/>
+      <c r="B173" s="96"/>
       <c r="C173" s="50" t="s">
         <v>1036</v>
       </c>
       <c r="D173" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E173" s="100" t="s">
+      <c r="E173" s="91" t="s">
         <v>1306</v>
       </c>
-      <c r="F173" s="106"/>
-      <c r="G173" s="106"/>
-      <c r="H173" s="101"/>
+      <c r="F173" s="98"/>
+      <c r="G173" s="98"/>
+      <c r="H173" s="92"/>
       <c r="I173" s="50">
         <v>2</v>
       </c>
     </row>
     <row r="174" spans="1:9" ht="51">
-      <c r="A174" s="90"/>
-      <c r="B174" s="90"/>
+      <c r="A174" s="114"/>
+      <c r="B174" s="114"/>
       <c r="C174" s="61" t="s">
         <v>1042</v>
       </c>
       <c r="D174" s="62" t="s">
         <v>1043</v>
       </c>
-      <c r="E174" s="104" t="s">
+      <c r="E174" s="100" t="s">
         <v>1307</v>
       </c>
-      <c r="F174" s="105"/>
+      <c r="F174" s="101"/>
       <c r="G174" s="62" t="s">
         <v>1308</v>
       </c>
@@ -29678,10 +29661,10 @@
       </c>
     </row>
     <row r="175" spans="1:9" ht="25.5">
-      <c r="A175" s="89" t="s">
+      <c r="A175" s="113" t="s">
         <v>1002</v>
       </c>
-      <c r="B175" s="89" t="s">
+      <c r="B175" s="113" t="s">
         <v>1003</v>
       </c>
       <c r="C175" s="58" t="s">
@@ -29707,75 +29690,75 @@
       </c>
     </row>
     <row r="176" spans="1:9" ht="12.75">
-      <c r="A176" s="87"/>
-      <c r="B176" s="87"/>
+      <c r="A176" s="96"/>
+      <c r="B176" s="96"/>
       <c r="C176" s="49" t="s">
         <v>1024</v>
       </c>
       <c r="D176" s="34" t="s">
         <v>1043</v>
       </c>
-      <c r="E176" s="100" t="s">
+      <c r="E176" s="91" t="s">
         <v>1329</v>
       </c>
-      <c r="F176" s="106"/>
-      <c r="G176" s="106"/>
-      <c r="H176" s="101"/>
+      <c r="F176" s="98"/>
+      <c r="G176" s="98"/>
+      <c r="H176" s="92"/>
       <c r="I176" s="50">
         <v>1</v>
       </c>
     </row>
     <row r="177" spans="1:9" ht="12.75">
-      <c r="A177" s="87"/>
-      <c r="B177" s="87"/>
+      <c r="A177" s="96"/>
+      <c r="B177" s="96"/>
       <c r="C177" s="49" t="s">
         <v>1030</v>
       </c>
       <c r="D177" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E177" s="100" t="s">
+      <c r="E177" s="91" t="s">
         <v>1330</v>
       </c>
-      <c r="F177" s="106"/>
-      <c r="G177" s="106"/>
-      <c r="H177" s="101"/>
+      <c r="F177" s="98"/>
+      <c r="G177" s="98"/>
+      <c r="H177" s="92"/>
       <c r="I177" s="50">
         <v>1</v>
       </c>
     </row>
     <row r="178" spans="1:9" ht="12.75">
-      <c r="A178" s="87"/>
-      <c r="B178" s="87"/>
+      <c r="A178" s="96"/>
+      <c r="B178" s="96"/>
       <c r="C178" s="50" t="s">
         <v>1036</v>
       </c>
       <c r="D178" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E178" s="100" t="s">
+      <c r="E178" s="91" t="s">
         <v>1306</v>
       </c>
-      <c r="F178" s="106"/>
-      <c r="G178" s="106"/>
-      <c r="H178" s="101"/>
+      <c r="F178" s="98"/>
+      <c r="G178" s="98"/>
+      <c r="H178" s="92"/>
       <c r="I178" s="50">
         <v>2</v>
       </c>
     </row>
     <row r="179" spans="1:9" ht="51">
-      <c r="A179" s="90"/>
-      <c r="B179" s="90"/>
+      <c r="A179" s="114"/>
+      <c r="B179" s="114"/>
       <c r="C179" s="61" t="s">
         <v>1042</v>
       </c>
       <c r="D179" s="62" t="s">
         <v>1043</v>
       </c>
-      <c r="E179" s="104" t="s">
+      <c r="E179" s="100" t="s">
         <v>1307</v>
       </c>
-      <c r="F179" s="105"/>
+      <c r="F179" s="101"/>
       <c r="G179" s="62" t="s">
         <v>1308</v>
       </c>
@@ -29787,10 +29770,10 @@
       </c>
     </row>
     <row r="180" spans="1:9" ht="25.5">
-      <c r="A180" s="89" t="s">
+      <c r="A180" s="113" t="s">
         <v>820</v>
       </c>
-      <c r="B180" s="89" t="s">
+      <c r="B180" s="113" t="s">
         <v>1004</v>
       </c>
       <c r="C180" s="58" t="s">
@@ -29816,75 +29799,75 @@
       </c>
     </row>
     <row r="181" spans="1:9" ht="12.75">
-      <c r="A181" s="87"/>
-      <c r="B181" s="87"/>
+      <c r="A181" s="96"/>
+      <c r="B181" s="96"/>
       <c r="C181" s="49" t="s">
         <v>1024</v>
       </c>
       <c r="D181" s="34" t="s">
         <v>1043</v>
       </c>
-      <c r="E181" s="100" t="s">
+      <c r="E181" s="91" t="s">
         <v>1331</v>
       </c>
-      <c r="F181" s="106"/>
-      <c r="G181" s="106"/>
-      <c r="H181" s="101"/>
+      <c r="F181" s="98"/>
+      <c r="G181" s="98"/>
+      <c r="H181" s="92"/>
       <c r="I181" s="50">
         <v>1</v>
       </c>
     </row>
     <row r="182" spans="1:9" ht="12.75">
-      <c r="A182" s="87"/>
-      <c r="B182" s="87"/>
+      <c r="A182" s="96"/>
+      <c r="B182" s="96"/>
       <c r="C182" s="49" t="s">
         <v>1030</v>
       </c>
       <c r="D182" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E182" s="100" t="s">
+      <c r="E182" s="91" t="s">
         <v>1330</v>
       </c>
-      <c r="F182" s="106"/>
-      <c r="G182" s="106"/>
-      <c r="H182" s="101"/>
+      <c r="F182" s="98"/>
+      <c r="G182" s="98"/>
+      <c r="H182" s="92"/>
       <c r="I182" s="50">
         <v>1</v>
       </c>
     </row>
     <row r="183" spans="1:9" ht="12.75">
-      <c r="A183" s="87"/>
-      <c r="B183" s="87"/>
+      <c r="A183" s="96"/>
+      <c r="B183" s="96"/>
       <c r="C183" s="50" t="s">
         <v>1036</v>
       </c>
       <c r="D183" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E183" s="100" t="s">
+      <c r="E183" s="91" t="s">
         <v>1306</v>
       </c>
-      <c r="F183" s="106"/>
-      <c r="G183" s="106"/>
-      <c r="H183" s="101"/>
+      <c r="F183" s="98"/>
+      <c r="G183" s="98"/>
+      <c r="H183" s="92"/>
       <c r="I183" s="50">
         <v>2</v>
       </c>
     </row>
     <row r="184" spans="1:9" ht="51">
-      <c r="A184" s="90"/>
-      <c r="B184" s="90"/>
+      <c r="A184" s="114"/>
+      <c r="B184" s="114"/>
       <c r="C184" s="61" t="s">
         <v>1042</v>
       </c>
       <c r="D184" s="62" t="s">
         <v>1043</v>
       </c>
-      <c r="E184" s="104" t="s">
+      <c r="E184" s="100" t="s">
         <v>1307</v>
       </c>
-      <c r="F184" s="105"/>
+      <c r="F184" s="101"/>
       <c r="G184" s="62" t="s">
         <v>1308</v>
       </c>
@@ -29896,10 +29879,10 @@
       </c>
     </row>
     <row r="185" spans="1:9" ht="25.5">
-      <c r="A185" s="89" t="s">
+      <c r="A185" s="113" t="s">
         <v>826</v>
       </c>
-      <c r="B185" s="89" t="s">
+      <c r="B185" s="113" t="s">
         <v>1005</v>
       </c>
       <c r="C185" s="58" t="s">
@@ -29925,75 +29908,75 @@
       </c>
     </row>
     <row r="186" spans="1:9" ht="12.75">
-      <c r="A186" s="87"/>
-      <c r="B186" s="87"/>
+      <c r="A186" s="96"/>
+      <c r="B186" s="96"/>
       <c r="C186" s="49" t="s">
         <v>1024</v>
       </c>
       <c r="D186" s="34" t="s">
         <v>1043</v>
       </c>
-      <c r="E186" s="100" t="s">
+      <c r="E186" s="91" t="s">
         <v>1332</v>
       </c>
-      <c r="F186" s="106"/>
-      <c r="G186" s="106"/>
-      <c r="H186" s="101"/>
+      <c r="F186" s="98"/>
+      <c r="G186" s="98"/>
+      <c r="H186" s="92"/>
       <c r="I186" s="50">
         <v>1</v>
       </c>
     </row>
     <row r="187" spans="1:9" ht="12.75">
-      <c r="A187" s="87"/>
-      <c r="B187" s="87"/>
+      <c r="A187" s="96"/>
+      <c r="B187" s="96"/>
       <c r="C187" s="49" t="s">
         <v>1030</v>
       </c>
       <c r="D187" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E187" s="100" t="s">
+      <c r="E187" s="91" t="s">
         <v>1333</v>
       </c>
-      <c r="F187" s="106"/>
-      <c r="G187" s="106"/>
-      <c r="H187" s="101"/>
+      <c r="F187" s="98"/>
+      <c r="G187" s="98"/>
+      <c r="H187" s="92"/>
       <c r="I187" s="50">
         <v>1</v>
       </c>
     </row>
     <row r="188" spans="1:9" ht="12.75">
-      <c r="A188" s="87"/>
-      <c r="B188" s="87"/>
+      <c r="A188" s="96"/>
+      <c r="B188" s="96"/>
       <c r="C188" s="50" t="s">
         <v>1036</v>
       </c>
       <c r="D188" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E188" s="100" t="s">
+      <c r="E188" s="91" t="s">
         <v>1317</v>
       </c>
-      <c r="F188" s="106"/>
-      <c r="G188" s="106"/>
-      <c r="H188" s="101"/>
+      <c r="F188" s="98"/>
+      <c r="G188" s="98"/>
+      <c r="H188" s="92"/>
       <c r="I188" s="50">
         <v>2</v>
       </c>
     </row>
     <row r="189" spans="1:9" ht="51">
-      <c r="A189" s="90"/>
-      <c r="B189" s="90"/>
+      <c r="A189" s="114"/>
+      <c r="B189" s="114"/>
       <c r="C189" s="61" t="s">
         <v>1042</v>
       </c>
       <c r="D189" s="62" t="s">
         <v>1043</v>
       </c>
-      <c r="E189" s="104" t="s">
+      <c r="E189" s="100" t="s">
         <v>1307</v>
       </c>
-      <c r="F189" s="105"/>
+      <c r="F189" s="101"/>
       <c r="G189" s="62" t="s">
         <v>1308</v>
       </c>
@@ -30005,10 +29988,10 @@
       </c>
     </row>
     <row r="190" spans="1:9" ht="25.5">
-      <c r="A190" s="89" t="s">
+      <c r="A190" s="113" t="s">
         <v>666</v>
       </c>
-      <c r="B190" s="89" t="s">
+      <c r="B190" s="113" t="s">
         <v>1006</v>
       </c>
       <c r="C190" s="58" t="s">
@@ -30034,75 +30017,75 @@
       </c>
     </row>
     <row r="191" spans="1:9" ht="12.75">
-      <c r="A191" s="87"/>
-      <c r="B191" s="87"/>
+      <c r="A191" s="96"/>
+      <c r="B191" s="96"/>
       <c r="C191" s="49" t="s">
         <v>1024</v>
       </c>
       <c r="D191" s="34" t="s">
         <v>1043</v>
       </c>
-      <c r="E191" s="100" t="s">
+      <c r="E191" s="91" t="s">
         <v>1334</v>
       </c>
-      <c r="F191" s="106"/>
-      <c r="G191" s="106"/>
-      <c r="H191" s="101"/>
+      <c r="F191" s="98"/>
+      <c r="G191" s="98"/>
+      <c r="H191" s="92"/>
       <c r="I191" s="50">
         <v>1</v>
       </c>
     </row>
     <row r="192" spans="1:9" ht="12.75">
-      <c r="A192" s="87"/>
-      <c r="B192" s="87"/>
+      <c r="A192" s="96"/>
+      <c r="B192" s="96"/>
       <c r="C192" s="49" t="s">
         <v>1030</v>
       </c>
       <c r="D192" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E192" s="100" t="s">
+      <c r="E192" s="91" t="s">
         <v>1333</v>
       </c>
-      <c r="F192" s="106"/>
-      <c r="G192" s="106"/>
-      <c r="H192" s="101"/>
+      <c r="F192" s="98"/>
+      <c r="G192" s="98"/>
+      <c r="H192" s="92"/>
       <c r="I192" s="50">
         <v>1</v>
       </c>
     </row>
     <row r="193" spans="1:9" ht="12.75">
-      <c r="A193" s="87"/>
-      <c r="B193" s="87"/>
+      <c r="A193" s="96"/>
+      <c r="B193" s="96"/>
       <c r="C193" s="50" t="s">
         <v>1036</v>
       </c>
       <c r="D193" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E193" s="100" t="s">
+      <c r="E193" s="91" t="s">
         <v>1317</v>
       </c>
-      <c r="F193" s="106"/>
-      <c r="G193" s="106"/>
-      <c r="H193" s="101"/>
+      <c r="F193" s="98"/>
+      <c r="G193" s="98"/>
+      <c r="H193" s="92"/>
       <c r="I193" s="50">
         <v>2</v>
       </c>
     </row>
     <row r="194" spans="1:9" ht="51">
-      <c r="A194" s="90"/>
-      <c r="B194" s="90"/>
+      <c r="A194" s="114"/>
+      <c r="B194" s="114"/>
       <c r="C194" s="61" t="s">
         <v>1042</v>
       </c>
       <c r="D194" s="62" t="s">
         <v>1043</v>
       </c>
-      <c r="E194" s="104" t="s">
+      <c r="E194" s="100" t="s">
         <v>1335</v>
       </c>
-      <c r="F194" s="105"/>
+      <c r="F194" s="101"/>
       <c r="G194" s="62" t="s">
         <v>1336</v>
       </c>
@@ -30114,10 +30097,10 @@
       </c>
     </row>
     <row r="195" spans="1:9" ht="25.5">
-      <c r="A195" s="89" t="s">
+      <c r="A195" s="113" t="s">
         <v>668</v>
       </c>
-      <c r="B195" s="89" t="s">
+      <c r="B195" s="113" t="s">
         <v>1007</v>
       </c>
       <c r="C195" s="58" t="s">
@@ -30143,75 +30126,75 @@
       </c>
     </row>
     <row r="196" spans="1:9" ht="12.75">
-      <c r="A196" s="87"/>
-      <c r="B196" s="87"/>
+      <c r="A196" s="96"/>
+      <c r="B196" s="96"/>
       <c r="C196" s="49" t="s">
         <v>1024</v>
       </c>
       <c r="D196" s="34" t="s">
         <v>1043</v>
       </c>
-      <c r="E196" s="100" t="s">
+      <c r="E196" s="91" t="s">
         <v>1338</v>
       </c>
-      <c r="F196" s="106"/>
-      <c r="G196" s="106"/>
-      <c r="H196" s="101"/>
+      <c r="F196" s="98"/>
+      <c r="G196" s="98"/>
+      <c r="H196" s="92"/>
       <c r="I196" s="50">
         <v>1</v>
       </c>
     </row>
     <row r="197" spans="1:9" ht="12.75">
-      <c r="A197" s="87"/>
-      <c r="B197" s="87"/>
+      <c r="A197" s="96"/>
+      <c r="B197" s="96"/>
       <c r="C197" s="49" t="s">
         <v>1030</v>
       </c>
       <c r="D197" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E197" s="100" t="s">
+      <c r="E197" s="91" t="s">
         <v>1339</v>
       </c>
-      <c r="F197" s="106"/>
-      <c r="G197" s="106"/>
-      <c r="H197" s="101"/>
+      <c r="F197" s="98"/>
+      <c r="G197" s="98"/>
+      <c r="H197" s="92"/>
       <c r="I197" s="50">
         <v>1</v>
       </c>
     </row>
     <row r="198" spans="1:9" ht="12.75">
-      <c r="A198" s="87"/>
-      <c r="B198" s="87"/>
+      <c r="A198" s="96"/>
+      <c r="B198" s="96"/>
       <c r="C198" s="50" t="s">
         <v>1036</v>
       </c>
       <c r="D198" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E198" s="100" t="s">
+      <c r="E198" s="91" t="s">
         <v>1317</v>
       </c>
-      <c r="F198" s="106"/>
-      <c r="G198" s="106"/>
-      <c r="H198" s="101"/>
+      <c r="F198" s="98"/>
+      <c r="G198" s="98"/>
+      <c r="H198" s="92"/>
       <c r="I198" s="50">
         <v>2</v>
       </c>
     </row>
     <row r="199" spans="1:9" ht="51">
-      <c r="A199" s="90"/>
-      <c r="B199" s="90"/>
+      <c r="A199" s="114"/>
+      <c r="B199" s="114"/>
       <c r="C199" s="61" t="s">
         <v>1042</v>
       </c>
       <c r="D199" s="62" t="s">
         <v>1043</v>
       </c>
-      <c r="E199" s="104" t="s">
+      <c r="E199" s="100" t="s">
         <v>1307</v>
       </c>
-      <c r="F199" s="105"/>
+      <c r="F199" s="101"/>
       <c r="G199" s="62" t="s">
         <v>1308</v>
       </c>
@@ -30223,10 +30206,10 @@
       </c>
     </row>
     <row r="200" spans="1:9" ht="25.5">
-      <c r="A200" s="89" t="s">
+      <c r="A200" s="113" t="s">
         <v>1340</v>
       </c>
-      <c r="B200" s="89" t="s">
+      <c r="B200" s="113" t="s">
         <v>1341</v>
       </c>
       <c r="C200" s="58" t="s">
@@ -30252,75 +30235,75 @@
       </c>
     </row>
     <row r="201" spans="1:9" ht="12.75">
-      <c r="A201" s="87"/>
-      <c r="B201" s="87"/>
+      <c r="A201" s="96"/>
+      <c r="B201" s="96"/>
       <c r="C201" s="49" t="s">
         <v>1024</v>
       </c>
       <c r="D201" s="34" t="s">
         <v>1043</v>
       </c>
-      <c r="E201" s="100" t="s">
+      <c r="E201" s="91" t="s">
         <v>1342</v>
       </c>
-      <c r="F201" s="106"/>
-      <c r="G201" s="106"/>
-      <c r="H201" s="101"/>
+      <c r="F201" s="98"/>
+      <c r="G201" s="98"/>
+      <c r="H201" s="92"/>
       <c r="I201" s="50">
         <v>1</v>
       </c>
     </row>
     <row r="202" spans="1:9" ht="12.75">
-      <c r="A202" s="87"/>
-      <c r="B202" s="87"/>
+      <c r="A202" s="96"/>
+      <c r="B202" s="96"/>
       <c r="C202" s="49" t="s">
         <v>1030</v>
       </c>
       <c r="D202" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E202" s="100" t="s">
+      <c r="E202" s="91" t="s">
         <v>1339</v>
       </c>
-      <c r="F202" s="106"/>
-      <c r="G202" s="106"/>
-      <c r="H202" s="101"/>
+      <c r="F202" s="98"/>
+      <c r="G202" s="98"/>
+      <c r="H202" s="92"/>
       <c r="I202" s="50">
         <v>1</v>
       </c>
     </row>
     <row r="203" spans="1:9" ht="12.75">
-      <c r="A203" s="87"/>
-      <c r="B203" s="87"/>
+      <c r="A203" s="96"/>
+      <c r="B203" s="96"/>
       <c r="C203" s="50" t="s">
         <v>1036</v>
       </c>
       <c r="D203" s="36" t="s">
         <v>1043</v>
       </c>
-      <c r="E203" s="100" t="s">
+      <c r="E203" s="91" t="s">
         <v>1317</v>
       </c>
-      <c r="F203" s="106"/>
-      <c r="G203" s="106"/>
-      <c r="H203" s="101"/>
+      <c r="F203" s="98"/>
+      <c r="G203" s="98"/>
+      <c r="H203" s="92"/>
       <c r="I203" s="50">
         <v>2</v>
       </c>
     </row>
     <row r="204" spans="1:9" ht="51">
-      <c r="A204" s="90"/>
-      <c r="B204" s="90"/>
+      <c r="A204" s="114"/>
+      <c r="B204" s="114"/>
       <c r="C204" s="61" t="s">
         <v>1042</v>
       </c>
       <c r="D204" s="62" t="s">
         <v>1043</v>
       </c>
-      <c r="E204" s="104" t="s">
+      <c r="E204" s="100" t="s">
         <v>1307</v>
       </c>
-      <c r="F204" s="105"/>
+      <c r="F204" s="101"/>
       <c r="G204" s="62" t="s">
         <v>1308</v>
       </c>
@@ -39089,71 +39072,162 @@
     </row>
   </sheetData>
   <mergeCells count="256">
-    <mergeCell ref="F95:G95"/>
-    <mergeCell ref="E96:H96"/>
-    <mergeCell ref="E85:H85"/>
-    <mergeCell ref="D86:H86"/>
-    <mergeCell ref="D87:E87"/>
-    <mergeCell ref="F87:H87"/>
-    <mergeCell ref="I89:I91"/>
-    <mergeCell ref="E92:F92"/>
-    <mergeCell ref="G92:H92"/>
-    <mergeCell ref="D93:E93"/>
-    <mergeCell ref="F93:G93"/>
-    <mergeCell ref="I93:I94"/>
-    <mergeCell ref="D94:E94"/>
-    <mergeCell ref="F94:G94"/>
-    <mergeCell ref="E80:F80"/>
-    <mergeCell ref="D81:E81"/>
-    <mergeCell ref="F81:G81"/>
-    <mergeCell ref="E72:H72"/>
-    <mergeCell ref="E73:H73"/>
-    <mergeCell ref="D74:H74"/>
-    <mergeCell ref="D75:E75"/>
-    <mergeCell ref="F75:H75"/>
-    <mergeCell ref="I77:I79"/>
-    <mergeCell ref="G80:H80"/>
-    <mergeCell ref="F70:G70"/>
-    <mergeCell ref="F71:G71"/>
-    <mergeCell ref="I65:I67"/>
-    <mergeCell ref="E68:F68"/>
-    <mergeCell ref="G68:H68"/>
-    <mergeCell ref="D69:E69"/>
-    <mergeCell ref="F69:G69"/>
-    <mergeCell ref="I69:I70"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="E48:H48"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="D50:H50"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="F51:H51"/>
-    <mergeCell ref="I53:I55"/>
-    <mergeCell ref="G56:H56"/>
-    <mergeCell ref="D63:E63"/>
-    <mergeCell ref="F63:H63"/>
-    <mergeCell ref="I57:I58"/>
-    <mergeCell ref="D58:E58"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="E60:H60"/>
-    <mergeCell ref="E61:H61"/>
-    <mergeCell ref="D62:H62"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="A4:A15"/>
-    <mergeCell ref="B4:B15"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="I41:I43"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="G44:H44"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="I45:I46"/>
-    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="A40:A51"/>
+    <mergeCell ref="B40:B51"/>
+    <mergeCell ref="A52:A63"/>
+    <mergeCell ref="B52:B63"/>
+    <mergeCell ref="A64:A75"/>
+    <mergeCell ref="B64:B75"/>
+    <mergeCell ref="B76:B87"/>
+    <mergeCell ref="A76:A87"/>
+    <mergeCell ref="A88:A99"/>
+    <mergeCell ref="A100:A104"/>
+    <mergeCell ref="A105:A109"/>
+    <mergeCell ref="A110:A116"/>
+    <mergeCell ref="A117:A123"/>
+    <mergeCell ref="A124:A129"/>
+    <mergeCell ref="B88:B99"/>
+    <mergeCell ref="B100:B104"/>
+    <mergeCell ref="B105:B109"/>
+    <mergeCell ref="B110:B116"/>
+    <mergeCell ref="B117:B123"/>
+    <mergeCell ref="B124:B129"/>
+    <mergeCell ref="B130:B134"/>
+    <mergeCell ref="A165:A169"/>
+    <mergeCell ref="A170:A174"/>
+    <mergeCell ref="A175:A179"/>
+    <mergeCell ref="A180:A184"/>
+    <mergeCell ref="A185:A189"/>
+    <mergeCell ref="A190:A194"/>
+    <mergeCell ref="A195:A199"/>
+    <mergeCell ref="A200:A204"/>
+    <mergeCell ref="A130:A134"/>
+    <mergeCell ref="A135:A139"/>
+    <mergeCell ref="A140:A144"/>
+    <mergeCell ref="A145:A149"/>
+    <mergeCell ref="A150:A154"/>
+    <mergeCell ref="A155:A159"/>
+    <mergeCell ref="A160:A164"/>
+    <mergeCell ref="B170:B174"/>
+    <mergeCell ref="B175:B179"/>
+    <mergeCell ref="B180:B184"/>
+    <mergeCell ref="B185:B189"/>
+    <mergeCell ref="B190:B194"/>
+    <mergeCell ref="B195:B199"/>
+    <mergeCell ref="B200:B204"/>
+    <mergeCell ref="B135:B139"/>
+    <mergeCell ref="B140:B144"/>
+    <mergeCell ref="B145:B149"/>
+    <mergeCell ref="B150:B154"/>
+    <mergeCell ref="B155:B159"/>
+    <mergeCell ref="B160:B164"/>
+    <mergeCell ref="B165:B169"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="E152:H152"/>
+    <mergeCell ref="E153:H153"/>
+    <mergeCell ref="E154:F154"/>
+    <mergeCell ref="E156:H156"/>
+    <mergeCell ref="E157:H157"/>
+    <mergeCell ref="E158:H158"/>
+    <mergeCell ref="E159:F159"/>
+    <mergeCell ref="G161:H161"/>
+    <mergeCell ref="E162:H162"/>
+    <mergeCell ref="E163:H163"/>
+    <mergeCell ref="E164:F164"/>
+    <mergeCell ref="E166:H166"/>
+    <mergeCell ref="A16:A27"/>
+    <mergeCell ref="B16:B27"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="D26:H26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="I29:I31"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="D38:H38"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F83:G83"/>
+    <mergeCell ref="E84:H84"/>
+    <mergeCell ref="E110:F110"/>
+    <mergeCell ref="E111:F111"/>
+    <mergeCell ref="E149:F149"/>
+    <mergeCell ref="E151:H151"/>
+    <mergeCell ref="E112:F112"/>
+    <mergeCell ref="E113:F113"/>
+    <mergeCell ref="I110:I116"/>
+    <mergeCell ref="I117:I123"/>
+    <mergeCell ref="E97:H97"/>
+    <mergeCell ref="D98:H98"/>
+    <mergeCell ref="D99:E99"/>
+    <mergeCell ref="F99:H99"/>
+    <mergeCell ref="I100:I104"/>
+    <mergeCell ref="I105:I109"/>
+    <mergeCell ref="E116:F116"/>
+    <mergeCell ref="E114:F114"/>
+    <mergeCell ref="E115:F115"/>
+    <mergeCell ref="E117:F117"/>
+    <mergeCell ref="E118:F118"/>
+    <mergeCell ref="E167:H167"/>
+    <mergeCell ref="E168:H168"/>
+    <mergeCell ref="E169:F169"/>
+    <mergeCell ref="E171:H171"/>
+    <mergeCell ref="E172:H172"/>
+    <mergeCell ref="E173:H173"/>
+    <mergeCell ref="E174:F174"/>
+    <mergeCell ref="E176:H176"/>
+    <mergeCell ref="E177:H177"/>
+    <mergeCell ref="E178:H178"/>
+    <mergeCell ref="E179:F179"/>
+    <mergeCell ref="E181:H181"/>
+    <mergeCell ref="E182:H182"/>
+    <mergeCell ref="E183:H183"/>
+    <mergeCell ref="E184:F184"/>
+    <mergeCell ref="E186:H186"/>
+    <mergeCell ref="E187:H187"/>
+    <mergeCell ref="E188:H188"/>
+    <mergeCell ref="E189:F189"/>
+    <mergeCell ref="E191:H191"/>
+    <mergeCell ref="E192:H192"/>
+    <mergeCell ref="E202:H202"/>
+    <mergeCell ref="E203:H203"/>
+    <mergeCell ref="E204:F204"/>
+    <mergeCell ref="E193:H193"/>
+    <mergeCell ref="E194:F194"/>
+    <mergeCell ref="E196:H196"/>
+    <mergeCell ref="E197:H197"/>
+    <mergeCell ref="E198:H198"/>
+    <mergeCell ref="E199:F199"/>
+    <mergeCell ref="E201:H201"/>
+    <mergeCell ref="E119:F119"/>
+    <mergeCell ref="E120:F120"/>
+    <mergeCell ref="E121:F121"/>
+    <mergeCell ref="E122:F122"/>
+    <mergeCell ref="E123:F123"/>
+    <mergeCell ref="E125:H125"/>
+    <mergeCell ref="E126:H126"/>
+    <mergeCell ref="E127:H127"/>
+    <mergeCell ref="E128:F128"/>
+    <mergeCell ref="E131:H131"/>
+    <mergeCell ref="E132:H132"/>
+    <mergeCell ref="E133:H133"/>
+    <mergeCell ref="E134:F134"/>
+    <mergeCell ref="E136:H136"/>
+    <mergeCell ref="E137:H137"/>
+    <mergeCell ref="E138:H138"/>
+    <mergeCell ref="E139:F139"/>
+    <mergeCell ref="E141:H141"/>
     <mergeCell ref="E142:H142"/>
     <mergeCell ref="E143:H143"/>
     <mergeCell ref="E144:F144"/>
@@ -39178,79 +39252,22 @@
     <mergeCell ref="E56:F56"/>
     <mergeCell ref="D57:E57"/>
     <mergeCell ref="F57:G57"/>
-    <mergeCell ref="E131:H131"/>
-    <mergeCell ref="E132:H132"/>
-    <mergeCell ref="E133:H133"/>
-    <mergeCell ref="E134:F134"/>
-    <mergeCell ref="E136:H136"/>
-    <mergeCell ref="E137:H137"/>
-    <mergeCell ref="E138:H138"/>
-    <mergeCell ref="E139:F139"/>
-    <mergeCell ref="E141:H141"/>
-    <mergeCell ref="E119:F119"/>
-    <mergeCell ref="E120:F120"/>
-    <mergeCell ref="E121:F121"/>
-    <mergeCell ref="E122:F122"/>
-    <mergeCell ref="E123:F123"/>
-    <mergeCell ref="E125:H125"/>
-    <mergeCell ref="E126:H126"/>
-    <mergeCell ref="E127:H127"/>
-    <mergeCell ref="E128:F128"/>
-    <mergeCell ref="E189:F189"/>
-    <mergeCell ref="E191:H191"/>
-    <mergeCell ref="E192:H192"/>
-    <mergeCell ref="E202:H202"/>
-    <mergeCell ref="E203:H203"/>
-    <mergeCell ref="E204:F204"/>
-    <mergeCell ref="E193:H193"/>
-    <mergeCell ref="E194:F194"/>
-    <mergeCell ref="E196:H196"/>
-    <mergeCell ref="E197:H197"/>
-    <mergeCell ref="E198:H198"/>
-    <mergeCell ref="E199:F199"/>
-    <mergeCell ref="E201:H201"/>
-    <mergeCell ref="E178:H178"/>
-    <mergeCell ref="E179:F179"/>
-    <mergeCell ref="E181:H181"/>
-    <mergeCell ref="E182:H182"/>
-    <mergeCell ref="E183:H183"/>
-    <mergeCell ref="E184:F184"/>
-    <mergeCell ref="E186:H186"/>
-    <mergeCell ref="E187:H187"/>
-    <mergeCell ref="E188:H188"/>
-    <mergeCell ref="E167:H167"/>
-    <mergeCell ref="E168:H168"/>
-    <mergeCell ref="E169:F169"/>
-    <mergeCell ref="E171:H171"/>
-    <mergeCell ref="E172:H172"/>
-    <mergeCell ref="E173:H173"/>
-    <mergeCell ref="E174:F174"/>
-    <mergeCell ref="E176:H176"/>
-    <mergeCell ref="E177:H177"/>
-    <mergeCell ref="I81:I82"/>
-    <mergeCell ref="D82:E82"/>
-    <mergeCell ref="F82:G82"/>
-    <mergeCell ref="F83:G83"/>
-    <mergeCell ref="E84:H84"/>
-    <mergeCell ref="E110:F110"/>
-    <mergeCell ref="E111:F111"/>
-    <mergeCell ref="E149:F149"/>
-    <mergeCell ref="E151:H151"/>
-    <mergeCell ref="E112:F112"/>
-    <mergeCell ref="E113:F113"/>
-    <mergeCell ref="I110:I116"/>
-    <mergeCell ref="I117:I123"/>
-    <mergeCell ref="E97:H97"/>
-    <mergeCell ref="D98:H98"/>
-    <mergeCell ref="D99:E99"/>
-    <mergeCell ref="F99:H99"/>
-    <mergeCell ref="I100:I104"/>
-    <mergeCell ref="I105:I109"/>
-    <mergeCell ref="E116:F116"/>
-    <mergeCell ref="E114:F114"/>
-    <mergeCell ref="E115:F115"/>
-    <mergeCell ref="E117:F117"/>
-    <mergeCell ref="E118:F118"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="A4:A15"/>
+    <mergeCell ref="B4:B15"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="I41:I43"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="I45:I46"/>
+    <mergeCell ref="D46:E46"/>
     <mergeCell ref="I33:I34"/>
     <mergeCell ref="D21:E21"/>
     <mergeCell ref="D22:E22"/>
@@ -39259,92 +39276,58 @@
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
     <mergeCell ref="D39:E39"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="E36:H36"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="D38:H38"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="A16:A27"/>
-    <mergeCell ref="B16:B27"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="D26:H26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="I29:I31"/>
-    <mergeCell ref="B140:B144"/>
-    <mergeCell ref="B145:B149"/>
-    <mergeCell ref="B150:B154"/>
-    <mergeCell ref="B155:B159"/>
-    <mergeCell ref="B160:B164"/>
-    <mergeCell ref="B165:B169"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="E152:H152"/>
-    <mergeCell ref="E153:H153"/>
-    <mergeCell ref="E154:F154"/>
-    <mergeCell ref="E156:H156"/>
-    <mergeCell ref="E157:H157"/>
-    <mergeCell ref="E158:H158"/>
-    <mergeCell ref="E159:F159"/>
-    <mergeCell ref="G161:H161"/>
-    <mergeCell ref="E162:H162"/>
-    <mergeCell ref="E163:H163"/>
-    <mergeCell ref="E164:F164"/>
-    <mergeCell ref="E166:H166"/>
-    <mergeCell ref="B130:B134"/>
-    <mergeCell ref="A165:A169"/>
-    <mergeCell ref="A170:A174"/>
-    <mergeCell ref="A175:A179"/>
-    <mergeCell ref="A180:A184"/>
-    <mergeCell ref="A185:A189"/>
-    <mergeCell ref="A190:A194"/>
-    <mergeCell ref="A195:A199"/>
-    <mergeCell ref="A200:A204"/>
-    <mergeCell ref="A130:A134"/>
-    <mergeCell ref="A135:A139"/>
-    <mergeCell ref="A140:A144"/>
-    <mergeCell ref="A145:A149"/>
-    <mergeCell ref="A150:A154"/>
-    <mergeCell ref="A155:A159"/>
-    <mergeCell ref="A160:A164"/>
-    <mergeCell ref="B170:B174"/>
-    <mergeCell ref="B175:B179"/>
-    <mergeCell ref="B180:B184"/>
-    <mergeCell ref="B185:B189"/>
-    <mergeCell ref="B190:B194"/>
-    <mergeCell ref="B195:B199"/>
-    <mergeCell ref="B200:B204"/>
-    <mergeCell ref="B135:B139"/>
-    <mergeCell ref="A100:A104"/>
-    <mergeCell ref="A105:A109"/>
-    <mergeCell ref="A110:A116"/>
-    <mergeCell ref="A117:A123"/>
-    <mergeCell ref="A124:A129"/>
-    <mergeCell ref="B88:B99"/>
-    <mergeCell ref="B100:B104"/>
-    <mergeCell ref="B105:B109"/>
-    <mergeCell ref="B110:B116"/>
-    <mergeCell ref="B117:B123"/>
-    <mergeCell ref="B124:B129"/>
-    <mergeCell ref="A40:A51"/>
-    <mergeCell ref="B40:B51"/>
-    <mergeCell ref="A52:A63"/>
-    <mergeCell ref="B52:B63"/>
-    <mergeCell ref="A64:A75"/>
-    <mergeCell ref="B64:B75"/>
-    <mergeCell ref="B76:B87"/>
-    <mergeCell ref="A76:A87"/>
-    <mergeCell ref="A88:A99"/>
+    <mergeCell ref="E48:H48"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="D50:H50"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="F51:H51"/>
+    <mergeCell ref="I53:I55"/>
+    <mergeCell ref="G56:H56"/>
+    <mergeCell ref="D63:E63"/>
+    <mergeCell ref="F63:H63"/>
+    <mergeCell ref="I57:I58"/>
+    <mergeCell ref="D58:E58"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="E60:H60"/>
+    <mergeCell ref="E61:H61"/>
+    <mergeCell ref="D62:H62"/>
+    <mergeCell ref="F70:G70"/>
+    <mergeCell ref="F71:G71"/>
+    <mergeCell ref="I65:I67"/>
+    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="G68:H68"/>
+    <mergeCell ref="D69:E69"/>
+    <mergeCell ref="F69:G69"/>
+    <mergeCell ref="I69:I70"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="E80:F80"/>
+    <mergeCell ref="D81:E81"/>
+    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="E72:H72"/>
+    <mergeCell ref="E73:H73"/>
+    <mergeCell ref="D74:H74"/>
+    <mergeCell ref="D75:E75"/>
+    <mergeCell ref="F75:H75"/>
+    <mergeCell ref="I77:I79"/>
+    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="I81:I82"/>
+    <mergeCell ref="D82:E82"/>
+    <mergeCell ref="F82:G82"/>
+    <mergeCell ref="F95:G95"/>
+    <mergeCell ref="E96:H96"/>
+    <mergeCell ref="E85:H85"/>
+    <mergeCell ref="D86:H86"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="F87:H87"/>
+    <mergeCell ref="I89:I91"/>
+    <mergeCell ref="E92:F92"/>
+    <mergeCell ref="G92:H92"/>
+    <mergeCell ref="D93:E93"/>
+    <mergeCell ref="F93:G93"/>
+    <mergeCell ref="I93:I94"/>
+    <mergeCell ref="D94:E94"/>
+    <mergeCell ref="F94:G94"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -39360,7 +39343,7 @@
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="38.5703125" customWidth="1"/>
-    <col min="2" max="2" width="10.28515625" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" customWidth="1"/>
     <col min="3" max="3" width="10.5703125" customWidth="1"/>
     <col min="4" max="4" width="11.140625" customWidth="1"/>
     <col min="5" max="5" width="19.140625" customWidth="1"/>
@@ -39541,7 +39524,7 @@
         <v>649</v>
       </c>
       <c r="K4" s="65">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L4" s="73"/>
       <c r="M4" s="73"/>
@@ -39669,7 +39652,7 @@
         <v>653</v>
       </c>
       <c r="K6" s="65">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L6" s="71"/>
       <c r="M6" s="71"/>
@@ -39730,7 +39713,7 @@
         <v>655</v>
       </c>
       <c r="K7" s="65">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N7" s="66" t="s">
         <v>1361</v>
@@ -39789,7 +39772,7 @@
         <v>657</v>
       </c>
       <c r="K8" s="65">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N8" s="66" t="s">
         <v>1361</v>
@@ -39850,7 +39833,7 @@
         <v>1383</v>
       </c>
       <c r="K9" s="65">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N9" s="66" t="s">
         <v>1361</v>
@@ -39909,7 +39892,7 @@
         <v>661</v>
       </c>
       <c r="K10" s="65">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N10" s="66" t="s">
         <v>1361</v>
@@ -39935,13 +39918,13 @@
         <v>1389</v>
       </c>
       <c r="B11" s="67">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="C11" s="67">
-        <v>0.25</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="D11" s="67">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="E11" s="69" t="s">
         <v>685</v>
@@ -39962,7 +39945,7 @@
         <v>1391</v>
       </c>
       <c r="K11" s="65">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="N11" s="66" t="s">
         <v>1361</v>
@@ -40015,7 +39998,7 @@
         <v>665</v>
       </c>
       <c r="K12" s="65">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N12" s="66" t="s">
         <v>1361</v>
@@ -40070,7 +40053,7 @@
         <v>667</v>
       </c>
       <c r="K13" s="65">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N13" s="66" t="s">
         <v>1361</v>
@@ -40085,9 +40068,9 @@
       <c r="T13" s="117" t="s">
         <v>1396</v>
       </c>
-      <c r="U13" s="109"/>
-      <c r="V13" s="109"/>
-      <c r="W13" s="109"/>
+      <c r="U13" s="94"/>
+      <c r="V13" s="94"/>
+      <c r="W13" s="94"/>
       <c r="X13" s="66"/>
       <c r="Y13" s="66"/>
       <c r="Z13" s="66"/>
@@ -40125,7 +40108,7 @@
         <v>669</v>
       </c>
       <c r="K14" s="65">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N14" s="66" t="s">
         <v>1362</v>
@@ -40140,9 +40123,9 @@
       <c r="T14" s="117" t="s">
         <v>1397</v>
       </c>
-      <c r="U14" s="109"/>
-      <c r="V14" s="109"/>
-      <c r="W14" s="109"/>
+      <c r="U14" s="94"/>
+      <c r="V14" s="94"/>
+      <c r="W14" s="94"/>
       <c r="X14" s="66"/>
       <c r="Y14" s="66"/>
       <c r="Z14" s="66"/>
@@ -40178,7 +40161,7 @@
       <c r="Z15" s="66"/>
       <c r="AA15" s="66"/>
     </row>
-    <row r="16" spans="1:27" ht="15.75" customHeight="1">
+    <row r="16" spans="1:27" ht="38.25">
       <c r="A16" s="75" t="s">
         <v>1401</v>
       </c>
@@ -40236,7 +40219,7 @@
       <c r="Z16" s="66"/>
       <c r="AA16" s="66"/>
     </row>
-    <row r="17" spans="1:27" ht="15.75" customHeight="1">
+    <row r="17" spans="1:27" ht="38.25">
       <c r="A17" s="65" t="s">
         <v>1413</v>
       </c>
@@ -40250,25 +40233,25 @@
         <v>715</v>
       </c>
       <c r="E17" s="77" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="F17" s="69" t="s">
         <v>724</v>
       </c>
       <c r="G17" s="77" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="H17" s="69" t="s">
         <v>732</v>
       </c>
       <c r="I17" s="77" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="J17" s="69" t="s">
         <v>740</v>
       </c>
       <c r="K17" s="77" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="L17" s="69" t="s">
         <v>748</v>
@@ -40282,7 +40265,7 @@
       <c r="P17" s="66"/>
       <c r="Q17" s="66"/>
       <c r="R17" s="66" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="S17" s="66"/>
       <c r="T17" s="66"/>
@@ -40294,12 +40277,12 @@
       <c r="Z17" s="66"/>
       <c r="AA17" s="66"/>
     </row>
-    <row r="18" spans="1:27" ht="15.75" customHeight="1">
+    <row r="18" spans="1:27" ht="51">
       <c r="A18" s="75" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="B18" s="75" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="C18" s="78">
         <v>0.1</v>
@@ -40338,13 +40321,13 @@
         <v>1379</v>
       </c>
       <c r="P18" s="66" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="Q18" s="66"/>
       <c r="R18" s="117" t="s">
-        <v>1424</v>
-      </c>
-      <c r="S18" s="109"/>
+        <v>1422</v>
+      </c>
+      <c r="S18" s="94"/>
       <c r="T18" s="66"/>
       <c r="U18" s="66"/>
       <c r="V18" s="66"/>
@@ -40354,39 +40337,39 @@
       <c r="Z18" s="66"/>
       <c r="AA18" s="66"/>
     </row>
-    <row r="19" spans="1:27" ht="15.75" customHeight="1">
+    <row r="19" spans="1:27" ht="38.25">
       <c r="A19" s="31" t="s">
+        <v>1423</v>
+      </c>
+      <c r="B19" s="75" t="s">
+        <v>1424</v>
+      </c>
+      <c r="C19" s="70" t="s">
         <v>1425</v>
-      </c>
-      <c r="B19" s="75" t="s">
-        <v>1426</v>
-      </c>
-      <c r="C19" s="70" t="s">
-        <v>1427</v>
       </c>
       <c r="D19" s="69" t="s">
         <v>720</v>
       </c>
-      <c r="E19" s="70" t="s">
-        <v>1428</v>
+      <c r="E19" s="77" t="s">
+        <v>1425</v>
       </c>
       <c r="F19" s="69" t="s">
         <v>728</v>
       </c>
-      <c r="G19" s="70" t="s">
-        <v>1429</v>
+      <c r="G19" s="77" t="s">
+        <v>1426</v>
       </c>
       <c r="H19" s="69" t="s">
         <v>736</v>
       </c>
-      <c r="I19" s="70" t="s">
-        <v>1430</v>
+      <c r="I19" s="77" t="s">
+        <v>1426</v>
       </c>
       <c r="J19" s="69" t="s">
         <v>744</v>
       </c>
-      <c r="K19" s="70" t="s">
-        <v>1431</v>
+      <c r="K19" s="77" t="s">
+        <v>1427</v>
       </c>
       <c r="L19" s="69" t="s">
         <v>752</v>
@@ -40398,13 +40381,13 @@
         <v>1384</v>
       </c>
       <c r="P19" s="66" t="s">
-        <v>1432</v>
+        <v>1428</v>
       </c>
       <c r="Q19" s="66"/>
       <c r="R19" s="117" t="s">
-        <v>1433</v>
-      </c>
-      <c r="S19" s="109"/>
+        <v>1429</v>
+      </c>
+      <c r="S19" s="94"/>
       <c r="T19" s="66"/>
       <c r="U19" s="66"/>
       <c r="V19" s="66"/>
@@ -40414,39 +40397,39 @@
       <c r="Z19" s="66"/>
       <c r="AA19" s="66"/>
     </row>
-    <row r="20" spans="1:27" ht="15.75" customHeight="1">
+    <row r="20" spans="1:27" ht="38.25">
       <c r="A20" s="36" t="s">
-        <v>1434</v>
+        <v>1430</v>
       </c>
       <c r="B20" s="75" t="s">
-        <v>1435</v>
+        <v>1431</v>
       </c>
       <c r="C20" s="77" t="s">
-        <v>1436</v>
+        <v>1432</v>
       </c>
       <c r="D20" s="69" t="s">
         <v>722</v>
       </c>
       <c r="E20" s="77" t="s">
-        <v>1437</v>
+        <v>1433</v>
       </c>
       <c r="F20" s="69" t="s">
         <v>730</v>
       </c>
       <c r="G20" s="77" t="s">
-        <v>1438</v>
+        <v>1434</v>
       </c>
       <c r="H20" s="69" t="s">
         <v>738</v>
       </c>
       <c r="I20" s="77" t="s">
-        <v>1439</v>
+        <v>1435</v>
       </c>
       <c r="J20" s="69" t="s">
         <v>746</v>
       </c>
       <c r="K20" s="77" t="s">
-        <v>1440</v>
+        <v>1436</v>
       </c>
       <c r="L20" s="69" t="s">
         <v>754</v>
@@ -40458,14 +40441,14 @@
         <v>1389</v>
       </c>
       <c r="P20" s="66" t="s">
-        <v>1441</v>
+        <v>1437</v>
       </c>
       <c r="Q20" s="66"/>
       <c r="R20" s="117" t="s">
-        <v>1442</v>
-      </c>
-      <c r="S20" s="109"/>
-      <c r="T20" s="109"/>
+        <v>1438</v>
+      </c>
+      <c r="S20" s="94"/>
+      <c r="T20" s="94"/>
       <c r="U20" s="66"/>
       <c r="V20" s="66"/>
       <c r="W20" s="66"/>
@@ -40484,10 +40467,10 @@
       <c r="P21" s="66"/>
       <c r="Q21" s="66"/>
       <c r="R21" s="117" t="s">
-        <v>1443</v>
-      </c>
-      <c r="S21" s="109"/>
-      <c r="T21" s="109"/>
+        <v>1439</v>
+      </c>
+      <c r="S21" s="94"/>
+      <c r="T21" s="94"/>
       <c r="U21" s="66"/>
       <c r="V21" s="66"/>
       <c r="W21" s="66"/>
@@ -40539,12 +40522,12 @@
       <c r="P22" s="66"/>
       <c r="Q22" s="66"/>
       <c r="R22" s="117" t="s">
-        <v>1444</v>
-      </c>
-      <c r="S22" s="109"/>
-      <c r="T22" s="109"/>
-      <c r="U22" s="109"/>
-      <c r="V22" s="109"/>
+        <v>1440</v>
+      </c>
+      <c r="S22" s="94"/>
+      <c r="T22" s="94"/>
+      <c r="U22" s="94"/>
+      <c r="V22" s="94"/>
       <c r="W22" s="66"/>
       <c r="X22" s="66"/>
       <c r="Y22" s="66"/>
@@ -40553,7 +40536,7 @@
     </row>
     <row r="23" spans="1:27" ht="15.75" customHeight="1">
       <c r="A23" s="65" t="s">
-        <v>1445</v>
+        <v>1441</v>
       </c>
       <c r="B23" s="67">
         <v>0.15</v>
@@ -40594,21 +40577,21 @@
       <c r="P23" s="66"/>
       <c r="Q23" s="66"/>
       <c r="R23" s="117" t="s">
-        <v>1446</v>
-      </c>
-      <c r="S23" s="109"/>
-      <c r="T23" s="109"/>
-      <c r="U23" s="109"/>
-      <c r="V23" s="109"/>
-      <c r="W23" s="109"/>
-      <c r="X23" s="109"/>
-      <c r="Y23" s="109"/>
-      <c r="Z23" s="109"/>
-      <c r="AA23" s="109"/>
+        <v>1442</v>
+      </c>
+      <c r="S23" s="94"/>
+      <c r="T23" s="94"/>
+      <c r="U23" s="94"/>
+      <c r="V23" s="94"/>
+      <c r="W23" s="94"/>
+      <c r="X23" s="94"/>
+      <c r="Y23" s="94"/>
+      <c r="Z23" s="94"/>
+      <c r="AA23" s="94"/>
     </row>
     <row r="24" spans="1:27" ht="15.75" customHeight="1">
       <c r="A24" s="65" t="s">
-        <v>1447</v>
+        <v>1443</v>
       </c>
       <c r="B24" s="67">
         <v>0.15</v>
@@ -40647,13 +40630,13 @@
         <v>1372</v>
       </c>
       <c r="P24" s="66" t="s">
-        <v>1448</v>
+        <v>1444</v>
       </c>
       <c r="Q24" s="66"/>
       <c r="R24" s="117" t="s">
-        <v>1449</v>
-      </c>
-      <c r="S24" s="109"/>
+        <v>1445</v>
+      </c>
+      <c r="S24" s="94"/>
       <c r="T24" s="66"/>
       <c r="U24" s="66"/>
       <c r="V24" s="66"/>
@@ -40665,7 +40648,7 @@
     </row>
     <row r="25" spans="1:27" ht="15.75" customHeight="1">
       <c r="A25" s="65" t="s">
-        <v>1450</v>
+        <v>1446</v>
       </c>
       <c r="B25" s="67">
         <v>0.1</v>
@@ -40718,7 +40701,7 @@
     </row>
     <row r="26" spans="1:27" ht="15.75" customHeight="1">
       <c r="A26" s="65" t="s">
-        <v>1451</v>
+        <v>1447</v>
       </c>
       <c r="B26" s="67">
         <v>0.1</v>
@@ -40771,7 +40754,7 @@
     </row>
     <row r="27" spans="1:27" ht="15.75" customHeight="1">
       <c r="A27" s="65" t="s">
-        <v>1452</v>
+        <v>1448</v>
       </c>
       <c r="B27" s="67">
         <v>0.1</v>
@@ -40810,7 +40793,7 @@
         <v>1379</v>
       </c>
       <c r="P27" s="66" t="s">
-        <v>1453</v>
+        <v>1449</v>
       </c>
       <c r="Q27" s="66"/>
       <c r="R27" s="66"/>
@@ -40826,16 +40809,16 @@
     </row>
     <row r="28" spans="1:27" ht="15.75" customHeight="1">
       <c r="A28" s="65" t="s">
-        <v>1454</v>
+        <v>1450</v>
       </c>
       <c r="B28" s="67">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="C28" s="67">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="D28" s="67">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="E28" s="69" t="s">
         <v>680</v>
@@ -40879,7 +40862,7 @@
     </row>
     <row r="29" spans="1:27" ht="15.75" customHeight="1">
       <c r="A29" s="75" t="s">
-        <v>1455</v>
+        <v>1451</v>
       </c>
       <c r="B29" s="67">
         <v>0.1</v>
@@ -40932,7 +40915,7 @@
     </row>
     <row r="30" spans="1:27" ht="15.75" customHeight="1">
       <c r="A30" s="65" t="s">
-        <v>1456</v>
+        <v>1452</v>
       </c>
       <c r="B30" s="67">
         <v>0.1</v>
@@ -40985,7 +40968,7 @@
     </row>
     <row r="31" spans="1:27" ht="15.75" customHeight="1">
       <c r="A31" s="65" t="s">
-        <v>1457</v>
+        <v>1453</v>
       </c>
       <c r="B31" s="67">
         <v>0.1</v>
@@ -41038,7 +41021,7 @@
     </row>
     <row r="32" spans="1:27" ht="15.75" customHeight="1">
       <c r="A32" s="65" t="s">
-        <v>1458</v>
+        <v>1454</v>
       </c>
       <c r="B32" s="80">
         <v>5</v>
@@ -41091,7 +41074,7 @@
     </row>
     <row r="33" spans="1:27" ht="15.75" customHeight="1">
       <c r="A33" s="65" t="s">
-        <v>1459</v>
+        <v>1455</v>
       </c>
       <c r="B33" s="65">
         <v>2</v>
@@ -41144,16 +41127,16 @@
     </row>
     <row r="34" spans="1:27" ht="15.75" customHeight="1">
       <c r="A34" s="81" t="s">
-        <v>1460</v>
+        <v>1456</v>
       </c>
       <c r="B34" s="82">
-        <v>0.55000000000000004</v>
+        <v>0.2</v>
       </c>
       <c r="C34" s="82">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="D34" s="67">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="E34" s="69" t="s">
         <v>690</v>
@@ -41195,12 +41178,12 @@
       <c r="Z34" s="66"/>
       <c r="AA34" s="66"/>
     </row>
-    <row r="35" spans="1:27" ht="15.75" customHeight="1">
+    <row r="35" spans="1:27" ht="14.25">
       <c r="A35" s="75" t="s">
-        <v>1461</v>
+        <v>1457</v>
       </c>
       <c r="B35" s="65" t="s">
-        <v>1462</v>
+        <v>1458</v>
       </c>
       <c r="C35" s="65"/>
       <c r="F35" s="30"/>
@@ -41211,7 +41194,7 @@
         <v>1379</v>
       </c>
       <c r="P35" s="66" t="s">
-        <v>1463</v>
+        <v>1459</v>
       </c>
       <c r="Q35" s="66"/>
       <c r="R35" s="66"/>
@@ -41225,9 +41208,9 @@
       <c r="Z35" s="66"/>
       <c r="AA35" s="66"/>
     </row>
-    <row r="36" spans="1:27" ht="15.75" customHeight="1">
+    <row r="36" spans="1:27" ht="38.25">
       <c r="A36" s="75" t="s">
-        <v>1464</v>
+        <v>1460</v>
       </c>
       <c r="B36" s="65" t="s">
         <v>1343</v>
@@ -41269,7 +41252,7 @@
         <v>1384</v>
       </c>
       <c r="P36" s="66" t="s">
-        <v>1465</v>
+        <v>1461</v>
       </c>
       <c r="Q36" s="66"/>
       <c r="R36" s="66"/>
@@ -41283,9 +41266,9 @@
       <c r="Z36" s="66"/>
       <c r="AA36" s="66"/>
     </row>
-    <row r="37" spans="1:27" ht="15.75" customHeight="1">
+    <row r="37" spans="1:27" ht="38.25">
       <c r="A37" s="65" t="s">
-        <v>1466</v>
+        <v>1462</v>
       </c>
       <c r="B37" s="75" t="s">
         <v>1414</v>
@@ -41339,12 +41322,12 @@
       <c r="Z37" s="66"/>
       <c r="AA37" s="66"/>
     </row>
-    <row r="38" spans="1:27" ht="15.75" customHeight="1">
+    <row r="38" spans="1:27" ht="38.25">
       <c r="A38" s="75" t="s">
-        <v>1467</v>
+        <v>1463</v>
       </c>
       <c r="B38" s="75" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="C38" s="78">
         <v>0.1</v>
@@ -41395,39 +41378,39 @@
       <c r="Z38" s="66"/>
       <c r="AA38" s="66"/>
     </row>
-    <row r="39" spans="1:27" ht="15.75" customHeight="1">
+    <row r="39" spans="1:27" ht="38.25">
       <c r="A39" s="31" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="B39" s="75" t="s">
-        <v>1468</v>
+        <v>1464</v>
       </c>
       <c r="C39" s="77" t="s">
-        <v>1436</v>
+        <v>1432</v>
       </c>
       <c r="D39" s="69" t="s">
         <v>720</v>
       </c>
       <c r="E39" s="77" t="s">
-        <v>1437</v>
+        <v>1433</v>
       </c>
       <c r="F39" s="69" t="s">
         <v>728</v>
       </c>
       <c r="G39" s="77" t="s">
-        <v>1437</v>
+        <v>1433</v>
       </c>
       <c r="H39" s="69" t="s">
         <v>736</v>
       </c>
       <c r="I39" s="77" t="s">
-        <v>1438</v>
+        <v>1433</v>
       </c>
       <c r="J39" s="69" t="s">
         <v>744</v>
       </c>
       <c r="K39" s="77" t="s">
-        <v>1438</v>
+        <v>1434</v>
       </c>
       <c r="L39" s="69" t="s">
         <v>752</v>
@@ -41439,7 +41422,7 @@
         <v>1393</v>
       </c>
       <c r="P39" s="66" t="s">
-        <v>1469</v>
+        <v>1465</v>
       </c>
       <c r="Q39" s="66"/>
       <c r="R39" s="66"/>
@@ -41453,39 +41436,39 @@
       <c r="Z39" s="66"/>
       <c r="AA39" s="66"/>
     </row>
-    <row r="40" spans="1:27" ht="15.75" customHeight="1">
+    <row r="40" spans="1:27" ht="38.25">
       <c r="A40" s="36" t="s">
-        <v>1470</v>
+        <v>1466</v>
       </c>
       <c r="B40" s="75" t="s">
-        <v>1435</v>
+        <v>1431</v>
       </c>
       <c r="C40" s="77" t="s">
-        <v>1436</v>
+        <v>1432</v>
       </c>
       <c r="D40" s="69" t="s">
         <v>722</v>
       </c>
       <c r="E40" s="77" t="s">
-        <v>1437</v>
+        <v>1433</v>
       </c>
       <c r="F40" s="69" t="s">
         <v>730</v>
       </c>
       <c r="G40" s="77" t="s">
-        <v>1438</v>
+        <v>1434</v>
       </c>
       <c r="H40" s="69" t="s">
         <v>738</v>
       </c>
       <c r="I40" s="77" t="s">
-        <v>1439</v>
+        <v>1435</v>
       </c>
       <c r="J40" s="69" t="s">
         <v>746</v>
       </c>
       <c r="K40" s="77" t="s">
-        <v>1440</v>
+        <v>1436</v>
       </c>
       <c r="L40" s="69" t="s">
         <v>754</v>
@@ -41497,7 +41480,7 @@
         <v>1395</v>
       </c>
       <c r="P40" s="66" t="s">
-        <v>1471</v>
+        <v>1467</v>
       </c>
       <c r="Q40" s="66"/>
       <c r="R40" s="66"/>
@@ -41519,7 +41502,7 @@
         <v>1376</v>
       </c>
       <c r="P41" s="66" t="s">
-        <v>1472</v>
+        <v>1468</v>
       </c>
       <c r="Q41" s="66"/>
       <c r="R41" s="66"/>
@@ -41541,7 +41524,7 @@
         <v>1379</v>
       </c>
       <c r="P42" s="66" t="s">
-        <v>1473</v>
+        <v>1469</v>
       </c>
       <c r="Q42" s="66"/>
       <c r="R42" s="66"/>
@@ -41583,7 +41566,7 @@
         <v>1389</v>
       </c>
       <c r="P44" s="66" t="s">
-        <v>1474</v>
+        <v>1470</v>
       </c>
       <c r="Q44" s="66"/>
       <c r="R44" s="66"/>
@@ -41645,7 +41628,7 @@
         <v>1395</v>
       </c>
       <c r="P47" s="66" t="s">
-        <v>1475</v>
+        <v>1471</v>
       </c>
       <c r="Q47" s="66"/>
       <c r="R47" s="66"/>
@@ -41667,7 +41650,7 @@
         <v>1379</v>
       </c>
       <c r="P48" s="66" t="s">
-        <v>1476</v>
+        <v>1472</v>
       </c>
       <c r="Q48" s="66"/>
       <c r="R48" s="66"/>
@@ -41709,7 +41692,7 @@
         <v>1389</v>
       </c>
       <c r="P50" s="66" t="s">
-        <v>1477</v>
+        <v>1473</v>
       </c>
       <c r="Q50" s="66"/>
       <c r="R50" s="66"/>
@@ -41732,7 +41715,7 @@
         <v>1392</v>
       </c>
       <c r="P51" s="66" t="s">
-        <v>1478</v>
+        <v>1474</v>
       </c>
       <c r="Q51" s="66"/>
       <c r="R51" s="66"/>
@@ -41755,7 +41738,7 @@
         <v>1393</v>
       </c>
       <c r="P52" s="66" t="s">
-        <v>1479</v>
+        <v>1475</v>
       </c>
       <c r="Q52" s="66"/>
       <c r="R52" s="66"/>
@@ -41799,7 +41782,7 @@
         <v>1384</v>
       </c>
       <c r="P54" s="66" t="s">
-        <v>1480</v>
+        <v>1476</v>
       </c>
       <c r="Q54" s="66"/>
       <c r="R54" s="66"/>
@@ -41822,7 +41805,7 @@
         <v>1389</v>
       </c>
       <c r="P55" s="66" t="s">
-        <v>1481</v>
+        <v>1477</v>
       </c>
       <c r="Q55" s="66"/>
       <c r="R55" s="66"/>
@@ -41845,7 +41828,7 @@
         <v>1392</v>
       </c>
       <c r="P56" s="66" t="s">
-        <v>1482</v>
+        <v>1478</v>
       </c>
       <c r="Q56" s="66"/>
       <c r="R56" s="66"/>
@@ -41868,7 +41851,7 @@
         <v>1393</v>
       </c>
       <c r="P57" s="66" t="s">
-        <v>1483</v>
+        <v>1479</v>
       </c>
       <c r="Q57" s="66"/>
       <c r="R57" s="66"/>
@@ -42017,7 +42000,7 @@
         <v>1393</v>
       </c>
       <c r="P64" s="66" t="s">
-        <v>1484</v>
+        <v>1480</v>
       </c>
       <c r="Q64" s="66"/>
       <c r="R64" s="66"/>
@@ -42040,7 +42023,7 @@
         <v>1395</v>
       </c>
       <c r="P65" s="66" t="s">
-        <v>1485</v>
+        <v>1481</v>
       </c>
       <c r="Q65" s="66"/>
       <c r="R65" s="66"/>
@@ -42063,7 +42046,7 @@
         <v>1393</v>
       </c>
       <c r="P66" s="66" t="s">
-        <v>1486</v>
+        <v>1482</v>
       </c>
       <c r="Q66" s="66"/>
       <c r="R66" s="66"/>
@@ -42142,7 +42125,7 @@
         <v>1343</v>
       </c>
       <c r="O70" s="66" t="s">
-        <v>1487</v>
+        <v>1483</v>
       </c>
       <c r="P70" s="66"/>
       <c r="Q70" s="66"/>
@@ -42163,7 +42146,7 @@
         <v>1361</v>
       </c>
       <c r="O71" s="66" t="s">
-        <v>1488</v>
+        <v>1484</v>
       </c>
       <c r="P71" s="66"/>
       <c r="Q71" s="66"/>
@@ -42184,7 +42167,7 @@
         <v>1362</v>
       </c>
       <c r="O72" s="66" t="s">
-        <v>1489</v>
+        <v>1485</v>
       </c>
       <c r="P72" s="66"/>
       <c r="Q72" s="66"/>
@@ -42205,7 +42188,7 @@
         <v>1367</v>
       </c>
       <c r="O73" s="66" t="s">
-        <v>1490</v>
+        <v>1486</v>
       </c>
       <c r="P73" s="66"/>
       <c r="Q73" s="66"/>
@@ -42226,7 +42209,7 @@
         <v>1372</v>
       </c>
       <c r="O74" s="66" t="s">
-        <v>1491</v>
+        <v>1487</v>
       </c>
       <c r="P74" s="66"/>
       <c r="Q74" s="66"/>
@@ -42247,7 +42230,7 @@
         <v>1375</v>
       </c>
       <c r="O75" s="66" t="s">
-        <v>1492</v>
+        <v>1488</v>
       </c>
       <c r="P75" s="66"/>
       <c r="Q75" s="66"/>
@@ -42268,7 +42251,7 @@
         <v>1376</v>
       </c>
       <c r="O76" s="66" t="s">
-        <v>1493</v>
+        <v>1489</v>
       </c>
       <c r="P76" s="66"/>
       <c r="Q76" s="66"/>
@@ -42289,7 +42272,7 @@
         <v>1379</v>
       </c>
       <c r="O77" s="66" t="s">
-        <v>1494</v>
+        <v>1490</v>
       </c>
       <c r="P77" s="66"/>
       <c r="Q77" s="66"/>
@@ -42310,7 +42293,7 @@
         <v>1384</v>
       </c>
       <c r="O78" s="66" t="s">
-        <v>1495</v>
+        <v>1491</v>
       </c>
       <c r="P78" s="66"/>
       <c r="Q78" s="66"/>
@@ -42331,7 +42314,7 @@
         <v>1389</v>
       </c>
       <c r="O79" s="66" t="s">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="P79" s="66"/>
       <c r="Q79" s="66"/>
@@ -42352,7 +42335,7 @@
         <v>1392</v>
       </c>
       <c r="O80" s="66" t="s">
-        <v>1497</v>
+        <v>1493</v>
       </c>
       <c r="P80" s="66"/>
       <c r="Q80" s="66"/>
@@ -42373,7 +42356,7 @@
         <v>1393</v>
       </c>
       <c r="O81" s="66" t="s">
-        <v>1498</v>
+        <v>1494</v>
       </c>
       <c r="P81" s="66"/>
       <c r="Q81" s="66"/>
@@ -42394,7 +42377,7 @@
         <v>1395</v>
       </c>
       <c r="O82" s="66" t="s">
-        <v>1499</v>
+        <v>1495</v>
       </c>
       <c r="P82" s="66"/>
       <c r="Q82" s="66"/>
